--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="200">
   <si>
     <t>Order ID</t>
   </si>
@@ -268,6 +268,15 @@
     <t>2026-04-17T19:37:57.927Z</t>
   </si>
   <si>
+    <t>ATH7818942656</t>
+  </si>
+  <si>
+    <t>Confirmed</t>
+  </si>
+  <si>
+    <t>2026-04-28T12:09:49.429Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -301,27 +310,30 @@
     <t>69df51939a28b213c15d5bfb</t>
   </si>
   <si>
+    <t>2026-04-28T12:17:31.160Z</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>VIP</t>
+  </si>
+  <si>
+    <t>69d8d572ae6a1e8c2c032bc2</t>
+  </si>
+  <si>
+    <t>Test User</t>
+  </si>
+  <si>
+    <t>testuser@example.com</t>
+  </si>
+  <si>
+    <t>0599999999</t>
+  </si>
+  <si>
     <t>New</t>
   </si>
   <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>VIP</t>
-  </si>
-  <si>
-    <t>69d8d572ae6a1e8c2c032bc2</t>
-  </si>
-  <si>
-    <t>Test User</t>
-  </si>
-  <si>
-    <t>testuser@example.com</t>
-  </si>
-  <si>
-    <t>0599999999</t>
-  </si>
-  <si>
     <t>69da482fe63ef65d62c51026</t>
   </si>
   <si>
@@ -565,6 +577,15 @@
     <t>Olive Square Jewelry Set</t>
   </si>
   <si>
+    <t>69f20e78c49efb1805c2fc83</t>
+  </si>
+  <si>
+    <t>Athar Golden Radiance Watch</t>
+  </si>
+  <si>
+    <t>2026-04-29T13:58:16.464Z</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -590,6 +611,9 @@
   </si>
   <si>
     <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
   </si>
 </sst>
 </file>
@@ -975,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -1846,6 +1870,47 @@
       </c>
       <c r="M21" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>120</v>
+      </c>
+      <c r="I22">
+        <v>120</v>
+      </c>
+      <c r="J22" t="s">
+        <v>85</v>
+      </c>
+      <c r="K22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22" t="s">
+        <v>86</v>
+      </c>
+      <c r="M22" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1870,39 +1935,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -1914,22 +1979,22 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>215</v>
+        <v>355</v>
       </c>
       <c r="G2" t="s">
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1961,7 +2026,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1993,21 +2058,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2025,21 +2090,21 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" t="s">
         <v>102</v>
       </c>
-      <c r="B6" t="s">
-        <v>99</v>
-      </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2057,44 +2122,44 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
         <v>105</v>
-      </c>
-      <c r="B7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2121,7 +2186,7 @@
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2132,19 +2197,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="19" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -2153,24 +2219,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -2191,12 +2257,12 @@
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -2205,24 +2271,24 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -2243,12 +2309,12 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -2269,12 +2335,12 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -2295,12 +2361,12 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -2321,12 +2387,12 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
@@ -2347,12 +2413,12 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
@@ -2373,12 +2439,12 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -2399,15 +2465,15 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
         <v>60</v>
@@ -2425,15 +2491,15 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -2451,15 +2517,15 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
@@ -2477,15 +2543,15 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C14" t="s">
         <v>60</v>
@@ -2503,15 +2569,15 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -2529,15 +2595,15 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -2555,15 +2621,15 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -2581,15 +2647,15 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -2607,18 +2673,18 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2633,18 +2699,18 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2659,18 +2725,18 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" t="s">
         <v>148</v>
-      </c>
-      <c r="C21" t="s">
-        <v>144</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -2685,15 +2751,15 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B22" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -2711,15 +2777,15 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -2737,15 +2803,15 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -2763,15 +2829,15 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -2789,15 +2855,15 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -2815,15 +2881,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2841,15 +2907,15 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -2867,15 +2933,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -2893,15 +2959,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
@@ -2919,15 +2985,15 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B31" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -2945,15 +3011,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -2971,15 +3037,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -2997,15 +3063,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -3023,15 +3089,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -3049,15 +3115,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B36" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -3075,15 +3141,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -3101,15 +3167,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -3127,7 +3193,33 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>120</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>187</v>
+      </c>
+      <c r="B39" t="s">
+        <v>188</v>
+      </c>
+      <c r="C39" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39">
+        <v>20</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
+        <v>189</v>
+      </c>
+      <c r="H39" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3138,7 +3230,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -3149,30 +3241,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -3195,7 +3287,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -3218,7 +3310,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -3241,7 +3333,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -3260,6 +3352,29 @@
       </c>
       <c r="G5">
         <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6">
+        <v>140</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="204">
   <si>
     <t>Order ID</t>
   </si>
@@ -277,6 +277,12 @@
     <t>2026-04-28T12:09:49.429Z</t>
   </si>
   <si>
+    <t>ATH4702950114</t>
+  </si>
+  <si>
+    <t>2026-05-01T14:50:29.508Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -352,6 +358,9 @@
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
+    <t>2026-05-01T14:50:30.330Z</t>
+  </si>
+  <si>
     <t>Product ID</t>
   </si>
   <si>
@@ -373,12 +382,15 @@
     <t>69d8ef134922394efe9aeddf</t>
   </si>
   <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>69d8ef144922394efe9aede2</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>69d8ef144922394efe9aede2</t>
-  </si>
-  <si>
     <t>69d8ef254922394efe9aedfe</t>
   </si>
   <si>
@@ -388,9 +400,6 @@
     <t>69d8ef1d4922394efe9aedf1</t>
   </si>
   <si>
-    <t>Critical</t>
-  </si>
-  <si>
     <t>69d8ef284922394efe9aee03</t>
   </si>
   <si>
@@ -614,6 +623,9 @@
   </si>
   <si>
     <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -1910,6 +1922,47 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>150</v>
+      </c>
+      <c r="I23">
+        <v>150</v>
+      </c>
+      <c r="J23" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1935,39 +1988,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -1988,13 +2041,13 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2026,7 +2079,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2058,21 +2111,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2090,54 +2143,54 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
         <v>107</v>
-      </c>
-      <c r="D6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" t="s">
         <v>110</v>
       </c>
-      <c r="D7" t="s">
-        <v>108</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
@@ -2154,12 +2207,12 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2171,22 +2224,22 @@
         <v>40</v>
       </c>
       <c r="E8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>1402</v>
+        <v>1572</v>
       </c>
       <c r="G8" t="s">
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2210,7 +2263,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -2219,24 +2272,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -2245,24 +2298,24 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -2283,12 +2336,12 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -2309,12 +2362,12 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -2335,12 +2388,12 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -2361,12 +2414,12 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -2387,12 +2440,12 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
@@ -2413,12 +2466,12 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
@@ -2439,12 +2492,12 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -2465,15 +2518,15 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
         <v>60</v>
@@ -2491,15 +2544,15 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -2517,15 +2570,15 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
@@ -2543,15 +2596,15 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
         <v>60</v>
@@ -2569,15 +2622,15 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -2595,15 +2648,15 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -2621,15 +2674,15 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B17" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -2647,15 +2700,15 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -2673,18 +2726,18 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2699,18 +2752,18 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2725,18 +2778,18 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" t="s">
         <v>151</v>
-      </c>
-      <c r="B21" t="s">
-        <v>152</v>
-      </c>
-      <c r="C21" t="s">
-        <v>148</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -2751,15 +2804,15 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -2777,15 +2830,15 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -2803,15 +2856,15 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -2829,15 +2882,15 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -2855,15 +2908,15 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -2881,15 +2934,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2907,15 +2960,15 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -2933,15 +2986,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B29" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -2959,15 +3012,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
@@ -2985,15 +3038,15 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -3011,15 +3064,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3037,15 +3090,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -3063,15 +3116,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -3089,15 +3142,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -3115,15 +3168,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -3141,15 +3194,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -3167,15 +3220,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -3193,18 +3246,18 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D39">
         <v>20</v>
@@ -3216,10 +3269,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H39" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3230,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -3241,30 +3294,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -3287,7 +3340,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -3310,7 +3363,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -3333,7 +3386,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -3356,7 +3409,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -3375,6 +3428,29 @@
       </c>
       <c r="G6">
         <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7">
+        <v>170</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="205">
   <si>
     <t>Order ID</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>2026-05-01T14:50:29.508Z</t>
+  </si>
+  <si>
+    <t>2026-05-01T14:51:54.558Z</t>
   </si>
   <si>
     <t>Customer ID</t>
@@ -1954,7 +1957,7 @@
         <v>150</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K23" t="s">
         <v>20</v>
@@ -1963,7 +1966,7 @@
         <v>88</v>
       </c>
       <c r="M23" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1988,39 +1991,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -2041,13 +2044,13 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2079,7 +2082,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2111,21 +2114,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2143,54 +2146,54 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
         <v>108</v>
-      </c>
-      <c r="B6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" t="s">
         <v>111</v>
       </c>
-      <c r="B7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" t="s">
-        <v>110</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
@@ -2207,12 +2210,12 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2233,13 +2236,13 @@
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2263,7 +2266,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -2272,24 +2275,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -2310,12 +2313,12 @@
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -2336,12 +2339,12 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -2362,12 +2365,12 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -2388,12 +2391,12 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -2414,12 +2417,12 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -2440,12 +2443,12 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
@@ -2466,12 +2469,12 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
@@ -2492,12 +2495,12 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -2518,15 +2521,15 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
         <v>60</v>
@@ -2544,15 +2547,15 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -2570,15 +2573,15 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
@@ -2596,15 +2599,15 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
         <v>60</v>
@@ -2622,15 +2625,15 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -2648,15 +2651,15 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -2674,15 +2677,15 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -2700,15 +2703,15 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -2726,18 +2729,18 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2752,18 +2755,18 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" t="s">
         <v>152</v>
-      </c>
-      <c r="B20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C20" t="s">
-        <v>151</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2778,18 +2781,18 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -2804,15 +2807,15 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -2830,15 +2833,15 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -2856,15 +2859,15 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -2882,15 +2885,15 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -2908,15 +2911,15 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -2934,15 +2937,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2960,15 +2963,15 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -2986,15 +2989,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -3012,15 +3015,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
@@ -3038,15 +3041,15 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -3064,15 +3067,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3090,15 +3093,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -3116,15 +3119,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -3142,15 +3145,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -3168,15 +3171,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -3194,15 +3197,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -3220,15 +3223,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -3246,18 +3249,18 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D39">
         <v>20</v>
@@ -3269,10 +3272,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3294,30 +3297,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -3340,7 +3343,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -3363,7 +3366,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -3386,7 +3389,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -3409,7 +3412,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -3432,7 +3435,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B7">
         <v>170</v>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="208">
   <si>
     <t>Order ID</t>
   </si>
@@ -286,6 +286,12 @@
     <t>2026-05-01T14:51:54.558Z</t>
   </si>
   <si>
+    <t>ATH3323452364</t>
+  </si>
+  <si>
+    <t>2026-05-03T18:33:54.528Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -361,7 +367,7 @@
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
-    <t>2026-05-01T14:50:30.330Z</t>
+    <t>2026-05-03T18:33:55.313Z</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -391,12 +397,12 @@
     <t>69d8ef144922394efe9aede2</t>
   </si>
   <si>
+    <t>69d8ef254922394efe9aedfe</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>69d8ef254922394efe9aedfe</t>
-  </si>
-  <si>
     <t>69d8ef134922394efe9aede0</t>
   </si>
   <si>
@@ -629,6 +635,9 @@
   </si>
   <si>
     <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -1967,6 +1976,47 @@
       </c>
       <c r="M23" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>120</v>
+      </c>
+      <c r="I24">
+        <v>120</v>
+      </c>
+      <c r="J24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" t="s">
+        <v>91</v>
+      </c>
+      <c r="M24" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1991,39 +2041,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -2044,13 +2094,13 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2082,7 +2132,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2114,21 +2164,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2146,54 +2196,54 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
         <v>110</v>
-      </c>
-      <c r="D6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" t="s">
         <v>113</v>
       </c>
-      <c r="D7" t="s">
-        <v>111</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
@@ -2210,12 +2260,12 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2227,22 +2277,22 @@
         <v>40</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>1572</v>
+        <v>1712</v>
       </c>
       <c r="G8" t="s">
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2266,7 +2316,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -2275,24 +2325,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -2313,12 +2363,12 @@
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -2327,13 +2377,13 @@
         <v>26</v>
       </c>
       <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
       <c r="F3">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -2344,7 +2394,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -2365,12 +2415,12 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -2391,12 +2441,12 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -2417,12 +2467,12 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -2443,12 +2493,12 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
@@ -2469,12 +2519,12 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
@@ -2495,12 +2545,12 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -2521,15 +2571,15 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
         <v>60</v>
@@ -2547,15 +2597,15 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -2573,15 +2623,15 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
@@ -2599,15 +2649,15 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C14" t="s">
         <v>60</v>
@@ -2625,15 +2675,15 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -2651,15 +2701,15 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -2677,15 +2727,15 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -2703,15 +2753,15 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -2729,18 +2779,18 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2755,18 +2805,18 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" t="s">
         <v>154</v>
-      </c>
-      <c r="C20" t="s">
-        <v>152</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2781,18 +2831,18 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -2807,15 +2857,15 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -2833,15 +2883,15 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -2859,15 +2909,15 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -2885,15 +2935,15 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -2911,15 +2961,15 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -2937,15 +2987,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2963,15 +3013,15 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -2989,15 +3039,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -3015,15 +3065,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
@@ -3041,15 +3091,15 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -3067,15 +3117,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3093,15 +3143,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -3119,15 +3169,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -3145,15 +3195,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -3171,15 +3221,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -3197,15 +3247,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -3223,15 +3273,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -3249,18 +3299,18 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D39">
         <v>20</v>
@@ -3272,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3286,7 +3336,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -3297,30 +3347,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -3343,7 +3393,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -3366,7 +3416,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -3389,7 +3439,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -3412,7 +3462,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -3435,7 +3485,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -3454,6 +3504,29 @@
       </c>
       <c r="G7">
         <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8">
+        <v>140</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="214">
   <si>
     <t>Order ID</t>
   </si>
@@ -286,6 +286,21 @@
     <t>2026-05-01T14:51:54.558Z</t>
   </si>
   <si>
+    <t>ATH3323452364</t>
+  </si>
+  <si>
+    <t>2026-05-03T18:33:54.528Z</t>
+  </si>
+  <si>
+    <t>2026-05-03T18:34:34.153Z</t>
+  </si>
+  <si>
+    <t>ATH3685738410</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:34:17.398Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -361,7 +376,7 @@
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
-    <t>2026-05-01T14:50:30.330Z</t>
+    <t>2026-05-03T19:34:18.614Z</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -391,12 +406,12 @@
     <t>69d8ef144922394efe9aede2</t>
   </si>
   <si>
+    <t>69d8ef254922394efe9aedfe</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>69d8ef254922394efe9aedfe</t>
-  </si>
-  <si>
     <t>69d8ef134922394efe9aede0</t>
   </si>
   <si>
@@ -598,6 +613,15 @@
     <t>2026-04-29T13:58:16.464Z</t>
   </si>
   <si>
+    <t>69f89d51987705d82e7eeaef</t>
+  </si>
+  <si>
+    <t>roro</t>
+  </si>
+  <si>
+    <t>2026-05-04T13:21:20.906Z</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -629,6 +653,9 @@
   </si>
   <si>
     <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -1967,6 +1994,88 @@
       </c>
       <c r="M23" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>120</v>
+      </c>
+      <c r="I24">
+        <v>120</v>
+      </c>
+      <c r="J24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" t="s">
+        <v>91</v>
+      </c>
+      <c r="M24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>120</v>
+      </c>
+      <c r="I25">
+        <v>120</v>
+      </c>
+      <c r="J25" t="s">
+        <v>85</v>
+      </c>
+      <c r="K25" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" t="s">
+        <v>94</v>
+      </c>
+      <c r="M25" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1991,39 +2100,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -2044,13 +2153,13 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2082,7 +2191,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2114,21 +2223,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2146,21 +2255,21 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2178,44 +2287,44 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
         <v>113</v>
-      </c>
-      <c r="D7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2227,22 +2336,22 @@
         <v>40</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>1572</v>
+        <v>1852</v>
       </c>
       <c r="G8" t="s">
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2253,7 +2362,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2266,7 +2375,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -2275,24 +2384,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -2313,12 +2422,12 @@
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -2327,24 +2436,24 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -2365,12 +2474,12 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -2391,12 +2500,12 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -2417,12 +2526,12 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -2443,12 +2552,12 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
@@ -2469,12 +2578,12 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
@@ -2495,12 +2604,12 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -2521,15 +2630,15 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C11" t="s">
         <v>60</v>
@@ -2547,15 +2656,15 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -2573,15 +2682,15 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
@@ -2599,15 +2708,15 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B14" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
         <v>60</v>
@@ -2625,15 +2734,15 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B15" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -2651,15 +2760,15 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -2677,15 +2786,15 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -2703,15 +2812,15 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -2729,18 +2838,18 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2755,18 +2864,18 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2781,18 +2890,18 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -2807,15 +2916,15 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -2833,15 +2942,15 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -2859,15 +2968,15 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -2885,15 +2994,15 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -2911,15 +3020,15 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -2937,15 +3046,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2963,15 +3072,15 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -2989,15 +3098,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -3015,15 +3124,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B30" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
@@ -3041,15 +3150,15 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -3067,15 +3176,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3093,15 +3202,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -3119,15 +3228,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -3145,15 +3254,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -3171,15 +3280,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B36" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -3197,15 +3306,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -3223,15 +3332,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B38" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -3249,18 +3358,18 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D39">
         <v>20</v>
@@ -3272,10 +3381,36 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H39" t="s">
-        <v>131</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40">
+        <v>20</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
+        <v>201</v>
+      </c>
+      <c r="H40" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3286,7 +3421,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -3297,30 +3432,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -3343,7 +3478,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -3366,7 +3501,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -3389,7 +3524,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -3412,7 +3547,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -3435,7 +3570,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -3454,6 +3589,29 @@
       </c>
       <c r="G7">
         <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8">
+        <v>280</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="238">
   <si>
     <t>Order ID</t>
   </si>
@@ -292,6 +292,87 @@
     <t>2026-05-03T18:33:54.528Z</t>
   </si>
   <si>
+    <t>2026-05-03T18:34:34.153Z</t>
+  </si>
+  <si>
+    <t>ATH3685738410</t>
+  </si>
+  <si>
+    <t>2026-05-03T19:34:17.398Z</t>
+  </si>
+  <si>
+    <t>ATH0702914363</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:03:49.150Z</t>
+  </si>
+  <si>
+    <t>ATH0703618564</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:03:56.186Z</t>
+  </si>
+  <si>
+    <t>ATH0707085075</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:04:30.851Z</t>
+  </si>
+  <si>
+    <t>ATH0712002761</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:05:20.028Z</t>
+  </si>
+  <si>
+    <t>ATH0715077389</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:05:50.774Z</t>
+  </si>
+  <si>
+    <t>ATH1908441937</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:24:44.427Z</t>
+  </si>
+  <si>
+    <t>ATH1908966379</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:24:49.664Z</t>
+  </si>
+  <si>
+    <t>ATH1912135035</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:25:21.352Z</t>
+  </si>
+  <si>
+    <t>ATH1926037538</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:27:40.376Z</t>
+  </si>
+  <si>
+    <t>ATH1931228735</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:28:32.295Z</t>
+  </si>
+  <si>
+    <t>ATH1937654837</t>
+  </si>
+  <si>
+    <t>Olive Branch Watch</t>
+  </si>
+  <si>
+    <t>Watches</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:29:36.549Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -367,7 +448,7 @@
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
-    <t>2026-05-03T18:33:55.313Z</t>
+    <t>2026-05-04T18:29:37.334Z</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -391,21 +472,27 @@
     <t>69d8ef134922394efe9aeddf</t>
   </si>
   <si>
+    <t>Out of Stock</t>
+  </si>
+  <si>
+    <t>69d8ef144922394efe9aede2</t>
+  </si>
+  <si>
+    <t>69d8ef134922394efe9aede0</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>69d8ef1b4922394efe9aeded</t>
+  </si>
+  <si>
     <t>Critical</t>
   </si>
   <si>
-    <t>69d8ef144922394efe9aede2</t>
-  </si>
-  <si>
     <t>69d8ef254922394efe9aedfe</t>
   </si>
   <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>69d8ef134922394efe9aede0</t>
-  </si>
-  <si>
     <t>69d8ef1d4922394efe9aedf1</t>
   </si>
   <si>
@@ -478,21 +565,12 @@
     <t>Citrus Orchard Watch</t>
   </si>
   <si>
-    <t>Watches</t>
-  </si>
-  <si>
     <t>69d8ef1b4922394efe9aedec</t>
   </si>
   <si>
     <t>Cedar Bloom Watch</t>
   </si>
   <si>
-    <t>69d8ef1b4922394efe9aeded</t>
-  </si>
-  <si>
-    <t>Olive Branch Watch</t>
-  </si>
-  <si>
     <t>69d8ef1c4922394efe9aedee</t>
   </si>
   <si>
@@ -604,6 +682,15 @@
     <t>2026-04-29T13:58:16.464Z</t>
   </si>
   <si>
+    <t>69f89d51987705d82e7eeaef</t>
+  </si>
+  <si>
+    <t>roro</t>
+  </si>
+  <si>
+    <t>2026-05-04T13:21:20.906Z</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -638,6 +725,9 @@
   </si>
   <si>
     <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -2007,7 +2097,7 @@
         <v>120</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K24" t="s">
         <v>20</v>
@@ -2016,6 +2106,498 @@
         <v>91</v>
       </c>
       <c r="M24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>120</v>
+      </c>
+      <c r="I25">
+        <v>120</v>
+      </c>
+      <c r="J25" t="s">
+        <v>85</v>
+      </c>
+      <c r="K25" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" t="s">
+        <v>94</v>
+      </c>
+      <c r="M25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>120</v>
+      </c>
+      <c r="I26">
+        <v>120</v>
+      </c>
+      <c r="J26" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" t="s">
+        <v>96</v>
+      </c>
+      <c r="M26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>120</v>
+      </c>
+      <c r="I27">
+        <v>120</v>
+      </c>
+      <c r="J27" t="s">
+        <v>85</v>
+      </c>
+      <c r="K27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" t="s">
+        <v>98</v>
+      </c>
+      <c r="M27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>120</v>
+      </c>
+      <c r="I28">
+        <v>120</v>
+      </c>
+      <c r="J28" t="s">
+        <v>85</v>
+      </c>
+      <c r="K28" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28" t="s">
+        <v>100</v>
+      </c>
+      <c r="M28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>150</v>
+      </c>
+      <c r="I29">
+        <v>150</v>
+      </c>
+      <c r="J29" t="s">
+        <v>85</v>
+      </c>
+      <c r="K29" t="s">
+        <v>20</v>
+      </c>
+      <c r="L29" t="s">
+        <v>102</v>
+      </c>
+      <c r="M29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>150</v>
+      </c>
+      <c r="I30">
+        <v>150</v>
+      </c>
+      <c r="J30" t="s">
+        <v>85</v>
+      </c>
+      <c r="K30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>150</v>
+      </c>
+      <c r="I31">
+        <v>150</v>
+      </c>
+      <c r="J31" t="s">
+        <v>85</v>
+      </c>
+      <c r="K31" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" t="s">
+        <v>106</v>
+      </c>
+      <c r="M31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>150</v>
+      </c>
+      <c r="I32">
+        <v>150</v>
+      </c>
+      <c r="J32" t="s">
+        <v>85</v>
+      </c>
+      <c r="K32" t="s">
+        <v>20</v>
+      </c>
+      <c r="L32" t="s">
+        <v>108</v>
+      </c>
+      <c r="M32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>60</v>
+      </c>
+      <c r="I33">
+        <v>60</v>
+      </c>
+      <c r="J33" t="s">
+        <v>85</v>
+      </c>
+      <c r="K33" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" t="s">
+        <v>110</v>
+      </c>
+      <c r="M33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>60</v>
+      </c>
+      <c r="I34">
+        <v>60</v>
+      </c>
+      <c r="J34" t="s">
+        <v>85</v>
+      </c>
+      <c r="K34" t="s">
+        <v>20</v>
+      </c>
+      <c r="L34" t="s">
+        <v>112</v>
+      </c>
+      <c r="M34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>60</v>
+      </c>
+      <c r="I35">
+        <v>60</v>
+      </c>
+      <c r="J35" t="s">
+        <v>85</v>
+      </c>
+      <c r="K35" t="s">
+        <v>20</v>
+      </c>
+      <c r="L35" t="s">
+        <v>114</v>
+      </c>
+      <c r="M35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" t="s">
+        <v>117</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>115</v>
+      </c>
+      <c r="I36">
+        <v>345</v>
+      </c>
+      <c r="J36" t="s">
+        <v>85</v>
+      </c>
+      <c r="K36" t="s">
+        <v>20</v>
+      </c>
+      <c r="L36" t="s">
+        <v>118</v>
+      </c>
+      <c r="M36" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2041,39 +2623,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -2094,13 +2676,13 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2132,7 +2714,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2164,21 +2746,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2196,21 +2778,21 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2228,21 +2810,21 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2260,12 +2842,12 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2277,22 +2859,22 @@
         <v>40</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>1712</v>
+        <v>3557</v>
       </c>
       <c r="G8" t="s">
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2303,7 +2885,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2316,7 +2898,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -2325,24 +2907,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -2351,24 +2933,24 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>1350</v>
+        <v>1950</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -2377,241 +2959,241 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>600</v>
+        <v>1080</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>212</v>
+        <v>360</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5">
-        <v>180</v>
+        <v>345</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
         <v>60</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -2623,21 +3205,21 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -2649,21 +3231,21 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -2675,21 +3257,21 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2701,21 +3283,21 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2727,21 +3309,21 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2753,21 +3335,21 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2779,21 +3361,21 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="C19" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2805,47 +3387,47 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
         <v>155</v>
-      </c>
-      <c r="B20" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" t="s">
-        <v>154</v>
-      </c>
-      <c r="D20">
-        <v>6</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2857,15 +3439,15 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -2883,15 +3465,15 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -2909,15 +3491,15 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -2935,15 +3517,15 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -2961,15 +3543,15 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="B26" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -2987,15 +3569,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -3013,15 +3595,15 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -3039,15 +3621,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -3065,15 +3647,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="B30" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
@@ -3091,15 +3673,15 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="B31" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -3117,15 +3699,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="B32" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3143,15 +3725,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -3169,15 +3751,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="B34" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -3195,15 +3777,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -3221,15 +3803,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="B36" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -3247,15 +3829,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="B37" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -3273,15 +3855,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="B38" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -3299,18 +3881,18 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C39" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="D39">
         <v>20</v>
@@ -3322,10 +3904,36 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="H39" t="s">
-        <v>133</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>222</v>
+      </c>
+      <c r="B40" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40">
+        <v>20</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
+        <v>224</v>
+      </c>
+      <c r="H40" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -3336,7 +3944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -3347,30 +3955,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -3393,7 +4001,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -3416,7 +4024,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -3439,7 +4047,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -3462,7 +4070,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -3485,7 +4093,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -3508,13 +4116,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="B8">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -3527,6 +4135,29 @@
       </c>
       <c r="G8">
         <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9">
+        <v>1705</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="246">
   <si>
     <t>Order ID</t>
   </si>
@@ -373,6 +373,33 @@
     <t>2026-05-04T18:29:36.549Z</t>
   </si>
   <si>
+    <t>ATH2041136067</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:46:51.361Z</t>
+  </si>
+  <si>
+    <t>ATH2044885659</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:47:28.858Z</t>
+  </si>
+  <si>
+    <t>ATH2048541897</t>
+  </si>
+  <si>
+    <t>Eight-Petal Flower Ring</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:48:05.421Z</t>
+  </si>
+  <si>
+    <t>ATH2596159649</t>
+  </si>
+  <si>
+    <t>2026-05-04T20:19:21.602Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -448,7 +475,7 @@
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
-    <t>2026-05-04T18:29:37.334Z</t>
+    <t>2026-05-04T20:19:22.520Z</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -481,18 +508,18 @@
     <t>69d8ef134922394efe9aede0</t>
   </si>
   <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>69d8ef1b4922394efe9aeded</t>
+  </si>
+  <si>
+    <t>69d8ef254922394efe9aedfe</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>69d8ef1b4922394efe9aeded</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>69d8ef254922394efe9aedfe</t>
-  </si>
-  <si>
     <t>69d8ef1d4922394efe9aedf1</t>
   </si>
   <si>
@@ -512,9 +539,6 @@
   </si>
   <si>
     <t>69d8ef144922394efe9aede1</t>
-  </si>
-  <si>
-    <t>Eight-Petal Flower Ring</t>
   </si>
   <si>
     <t>69d8ef154922394efe9aede3</t>
@@ -1113,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -2598,6 +2622,170 @@
         <v>118</v>
       </c>
       <c r="M36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>60</v>
+      </c>
+      <c r="I37">
+        <v>60</v>
+      </c>
+      <c r="J37" t="s">
+        <v>85</v>
+      </c>
+      <c r="K37" t="s">
+        <v>20</v>
+      </c>
+      <c r="L37" t="s">
+        <v>120</v>
+      </c>
+      <c r="M37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>60</v>
+      </c>
+      <c r="I38">
+        <v>60</v>
+      </c>
+      <c r="J38" t="s">
+        <v>85</v>
+      </c>
+      <c r="K38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38" t="s">
+        <v>122</v>
+      </c>
+      <c r="M38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>50</v>
+      </c>
+      <c r="I39">
+        <v>50</v>
+      </c>
+      <c r="J39" t="s">
+        <v>85</v>
+      </c>
+      <c r="K39" t="s">
+        <v>20</v>
+      </c>
+      <c r="L39" t="s">
+        <v>125</v>
+      </c>
+      <c r="M39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>60</v>
+      </c>
+      <c r="I40">
+        <v>60</v>
+      </c>
+      <c r="J40" t="s">
+        <v>85</v>
+      </c>
+      <c r="K40" t="s">
+        <v>20</v>
+      </c>
+      <c r="L40" t="s">
+        <v>127</v>
+      </c>
+      <c r="M40" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2623,39 +2811,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -2676,13 +2864,13 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2714,7 +2902,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2746,21 +2934,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2778,21 +2966,21 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2810,21 +2998,21 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2842,12 +3030,12 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2859,22 +3047,22 @@
         <v>40</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>3557</v>
+        <v>3867</v>
       </c>
       <c r="G8" t="s">
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2898,7 +3086,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -2907,24 +3095,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -2945,12 +3133,12 @@
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -2971,12 +3159,12 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
@@ -2985,24 +3173,24 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
         <v>116</v>
@@ -3023,12 +3211,12 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B6" t="s">
         <v>48</v>
@@ -3049,12 +3237,12 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -3075,12 +3263,12 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -3101,12 +3289,12 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
@@ -3127,12 +3315,12 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
@@ -3153,12 +3341,12 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B11" t="s">
         <v>59</v>
@@ -3179,41 +3367,41 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
         <v>60</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -3231,15 +3419,15 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
         <v>29</v>
@@ -3257,15 +3445,15 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
         <v>60</v>
@@ -3283,15 +3471,15 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
@@ -3309,15 +3497,15 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -3335,15 +3523,15 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -3361,15 +3549,15 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B19" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -3387,15 +3575,15 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C20" t="s">
         <v>117</v>
@@ -3413,15 +3601,15 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C21" t="s">
         <v>117</v>
@@ -3439,15 +3627,15 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B22" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -3465,15 +3653,15 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B23" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -3491,15 +3679,15 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -3517,15 +3705,15 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -3543,15 +3731,15 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -3569,15 +3757,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -3595,15 +3783,15 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B28" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -3621,15 +3809,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B29" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -3647,15 +3835,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B30" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
@@ -3673,15 +3861,15 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B31" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -3699,15 +3887,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B32" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3725,15 +3913,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B33" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -3751,15 +3939,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B34" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -3777,15 +3965,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -3803,15 +3991,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B36" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -3829,15 +4017,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B37" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -3855,15 +4043,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B38" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -3881,15 +4069,15 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C39" t="s">
         <v>117</v>
@@ -3904,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="H39" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B40" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C40" t="s">
         <v>23</v>
@@ -3930,10 +4118,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3955,30 +4143,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -4001,7 +4189,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -4024,7 +4212,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -4047,7 +4235,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -4070,7 +4258,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -4093,7 +4281,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -4116,7 +4304,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -4139,13 +4327,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B9">
-        <v>1705</v>
+        <v>2015</v>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4157,7 +4345,7 @@
         <v>18</v>
       </c>
       <c r="G9">
-        <v>155</v>
+        <v>134.33</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="250">
   <si>
     <t>Order ID</t>
   </si>
@@ -400,6 +400,18 @@
     <t>2026-05-04T20:19:21.602Z</t>
   </si>
   <si>
+    <t>ATH2636230029</t>
+  </si>
+  <si>
+    <t>2026-05-04T20:26:02.307Z</t>
+  </si>
+  <si>
+    <t>ATH2683918667</t>
+  </si>
+  <si>
+    <t>2026-05-04T20:33:59.194Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -475,7 +487,7 @@
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
-    <t>2026-05-04T20:19:22.520Z</t>
+    <t>2026-05-04T20:34:00.518Z</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -1137,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -2786,6 +2798,88 @@
         <v>127</v>
       </c>
       <c r="M40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" t="s">
+        <v>55</v>
+      </c>
+      <c r="F41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>95</v>
+      </c>
+      <c r="I41">
+        <v>95</v>
+      </c>
+      <c r="J41" t="s">
+        <v>85</v>
+      </c>
+      <c r="K41" t="s">
+        <v>20</v>
+      </c>
+      <c r="L41" t="s">
+        <v>129</v>
+      </c>
+      <c r="M41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>130</v>
+      </c>
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>94</v>
+      </c>
+      <c r="I42">
+        <v>94</v>
+      </c>
+      <c r="J42" t="s">
+        <v>85</v>
+      </c>
+      <c r="K42" t="s">
+        <v>20</v>
+      </c>
+      <c r="L42" t="s">
+        <v>131</v>
+      </c>
+      <c r="M42" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2811,39 +2905,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -2864,13 +2958,13 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2902,7 +2996,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2934,21 +3028,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2966,21 +3060,21 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" t="s">
         <v>147</v>
       </c>
-      <c r="B6" t="s">
-        <v>143</v>
-      </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2998,44 +3092,44 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
         <v>150</v>
-      </c>
-      <c r="B7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -3047,22 +3141,22 @@
         <v>40</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>3867</v>
+        <v>4056</v>
       </c>
       <c r="G8" t="s">
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3086,7 +3180,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -3095,24 +3189,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -3133,12 +3227,12 @@
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -3159,12 +3253,12 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
@@ -3185,12 +3279,12 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s">
         <v>116</v>
@@ -3211,12 +3305,12 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
         <v>48</v>
@@ -3237,12 +3331,12 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -3251,24 +3345,24 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -3277,24 +3371,24 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
@@ -3315,12 +3409,12 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
@@ -3341,12 +3435,12 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B11" t="s">
         <v>59</v>
@@ -3367,12 +3461,12 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B12" t="s">
         <v>124</v>
@@ -3393,15 +3487,15 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -3419,15 +3513,15 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
         <v>29</v>
@@ -3445,15 +3539,15 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
         <v>60</v>
@@ -3471,15 +3565,15 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
@@ -3497,15 +3591,15 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -3523,15 +3617,15 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -3549,15 +3643,15 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -3575,15 +3669,15 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C20" t="s">
         <v>117</v>
@@ -3601,15 +3695,15 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C21" t="s">
         <v>117</v>
@@ -3627,15 +3721,15 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B22" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -3653,15 +3747,15 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B23" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -3679,15 +3773,15 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B24" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -3705,15 +3799,15 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -3731,15 +3825,15 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B26" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -3757,15 +3851,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -3783,15 +3877,15 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B28" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -3809,15 +3903,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -3835,15 +3929,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
@@ -3861,15 +3955,15 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -3887,15 +3981,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3913,15 +4007,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -3939,15 +4033,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -3965,15 +4059,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B35" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -3991,15 +4085,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B36" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -4017,15 +4111,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B37" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -4043,15 +4137,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B38" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -4069,15 +4163,15 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B39" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C39" t="s">
         <v>117</v>
@@ -4092,18 +4186,18 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H39" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B40" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C40" t="s">
         <v>23</v>
@@ -4118,10 +4212,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H40" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -4143,30 +4237,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -4189,7 +4283,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -4212,7 +4306,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -4235,7 +4329,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -4258,7 +4352,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -4281,7 +4375,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -4304,7 +4398,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -4327,13 +4421,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B9">
-        <v>2015</v>
+        <v>2204</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4345,7 +4439,7 @@
         <v>18</v>
       </c>
       <c r="G9">
-        <v>134.33</v>
+        <v>129.65</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="262">
   <si>
     <t>Order ID</t>
   </si>
@@ -301,6 +301,156 @@
     <t>2026-05-03T19:34:17.398Z</t>
   </si>
   <si>
+    <t>ATH0702914363</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:03:49.150Z</t>
+  </si>
+  <si>
+    <t>ATH0703618564</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:03:56.186Z</t>
+  </si>
+  <si>
+    <t>ATH0707085075</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:04:30.851Z</t>
+  </si>
+  <si>
+    <t>ATH0712002761</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:05:20.028Z</t>
+  </si>
+  <si>
+    <t>ATH0715077389</t>
+  </si>
+  <si>
+    <t>2026-05-04T15:05:50.774Z</t>
+  </si>
+  <si>
+    <t>ATH1908441937</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:24:44.427Z</t>
+  </si>
+  <si>
+    <t>ATH1908966379</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:24:49.664Z</t>
+  </si>
+  <si>
+    <t>ATH1912135035</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:25:21.352Z</t>
+  </si>
+  <si>
+    <t>ATH1926037538</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:27:40.376Z</t>
+  </si>
+  <si>
+    <t>ATH1931228735</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:28:32.295Z</t>
+  </si>
+  <si>
+    <t>ATH1937654837</t>
+  </si>
+  <si>
+    <t>Olive Branch Watch</t>
+  </si>
+  <si>
+    <t>Watches</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:29:36.549Z</t>
+  </si>
+  <si>
+    <t>ATH2041136067</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:46:51.361Z</t>
+  </si>
+  <si>
+    <t>ATH2044885659</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:47:28.858Z</t>
+  </si>
+  <si>
+    <t>ATH2048541897</t>
+  </si>
+  <si>
+    <t>Eight-Petal Flower Ring</t>
+  </si>
+  <si>
+    <t>2026-05-04T18:48:05.421Z</t>
+  </si>
+  <si>
+    <t>ATH2596159649</t>
+  </si>
+  <si>
+    <t>2026-05-04T20:19:21.602Z</t>
+  </si>
+  <si>
+    <t>ATH2636230029</t>
+  </si>
+  <si>
+    <t>2026-05-04T20:26:02.307Z</t>
+  </si>
+  <si>
+    <t>ATH2683918667</t>
+  </si>
+  <si>
+    <t>2026-05-04T20:33:59.194Z</t>
+  </si>
+  <si>
+    <t>ATH2390836574</t>
+  </si>
+  <si>
+    <t>2026-05-04T19:45:08.372Z</t>
+  </si>
+  <si>
+    <t>ATH2403975287</t>
+  </si>
+  <si>
+    <t>2026-05-04T19:47:19.754Z</t>
+  </si>
+  <si>
+    <t>ATH2770081328</t>
+  </si>
+  <si>
+    <t>2026-05-04T20:48:20.815Z</t>
+  </si>
+  <si>
+    <t>ATH2416012187</t>
+  </si>
+  <si>
+    <t>Floral Link Bracelet</t>
+  </si>
+  <si>
+    <t>2026-05-04T19:49:20.123Z</t>
+  </si>
+  <si>
+    <t>ATH2436239317</t>
+  </si>
+  <si>
+    <t>2026-05-04T19:52:42.395Z</t>
+  </si>
+  <si>
+    <t>ATH3264015680</t>
+  </si>
+  <si>
+    <t>2026-05-04T22:10:40.162Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -376,7 +526,7 @@
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
-    <t>2026-05-03T19:34:18.614Z</t>
+    <t>2026-05-04T22:10:41.075Z</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -400,10 +550,25 @@
     <t>69d8ef134922394efe9aeddf</t>
   </si>
   <si>
+    <t>Out of Stock</t>
+  </si>
+  <si>
+    <t>69d8ef144922394efe9aede2</t>
+  </si>
+  <si>
+    <t>69d8ef134922394efe9aede0</t>
+  </si>
+  <si>
     <t>Critical</t>
   </si>
   <si>
-    <t>69d8ef144922394efe9aede2</t>
+    <t>69d8ef284922394efe9aee03</t>
+  </si>
+  <si>
+    <t>69d8ef1b4922394efe9aeded</t>
+  </si>
+  <si>
+    <t>69d8ef1d4922394efe9aedf1</t>
   </si>
   <si>
     <t>69d8ef254922394efe9aedfe</t>
@@ -412,13 +577,7 @@
     <t>Low</t>
   </si>
   <si>
-    <t>69d8ef134922394efe9aede0</t>
-  </si>
-  <si>
-    <t>69d8ef1d4922394efe9aedf1</t>
-  </si>
-  <si>
-    <t>69d8ef284922394efe9aee03</t>
+    <t>69d8ef144922394efe9aede1</t>
   </si>
   <si>
     <t>69d8ef264922394efe9aee00</t>
@@ -433,10 +592,7 @@
     <t>69d8ef254922394efe9aedff</t>
   </si>
   <si>
-    <t>69d8ef144922394efe9aede1</t>
-  </si>
-  <si>
-    <t>Eight-Petal Flower Ring</t>
+    <t>69d8ef214922394efe9aedf8</t>
   </si>
   <si>
     <t>69d8ef154922394efe9aede3</t>
@@ -487,21 +643,12 @@
     <t>Citrus Orchard Watch</t>
   </si>
   <si>
-    <t>Watches</t>
-  </si>
-  <si>
     <t>69d8ef1b4922394efe9aedec</t>
   </si>
   <si>
     <t>Cedar Bloom Watch</t>
   </si>
   <si>
-    <t>69d8ef1b4922394efe9aeded</t>
-  </si>
-  <si>
-    <t>Olive Branch Watch</t>
-  </si>
-  <si>
     <t>69d8ef1c4922394efe9aedee</t>
   </si>
   <si>
@@ -556,12 +703,6 @@
     <t>Grape Motif Ring Set</t>
   </si>
   <si>
-    <t>69d8ef214922394efe9aedf8</t>
-  </si>
-  <si>
-    <t>Floral Link Bracelet</t>
-  </si>
-  <si>
     <t>69d8ef224922394efe9aedf9</t>
   </si>
   <si>
@@ -656,6 +797,9 @@
   </si>
   <si>
     <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -2075,6 +2219,949 @@
         <v>94</v>
       </c>
       <c r="M25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>120</v>
+      </c>
+      <c r="I26">
+        <v>120</v>
+      </c>
+      <c r="J26" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" t="s">
+        <v>96</v>
+      </c>
+      <c r="M26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>120</v>
+      </c>
+      <c r="I27">
+        <v>120</v>
+      </c>
+      <c r="J27" t="s">
+        <v>85</v>
+      </c>
+      <c r="K27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" t="s">
+        <v>98</v>
+      </c>
+      <c r="M27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>120</v>
+      </c>
+      <c r="I28">
+        <v>120</v>
+      </c>
+      <c r="J28" t="s">
+        <v>85</v>
+      </c>
+      <c r="K28" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28" t="s">
+        <v>100</v>
+      </c>
+      <c r="M28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>150</v>
+      </c>
+      <c r="I29">
+        <v>150</v>
+      </c>
+      <c r="J29" t="s">
+        <v>85</v>
+      </c>
+      <c r="K29" t="s">
+        <v>20</v>
+      </c>
+      <c r="L29" t="s">
+        <v>102</v>
+      </c>
+      <c r="M29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>150</v>
+      </c>
+      <c r="I30">
+        <v>150</v>
+      </c>
+      <c r="J30" t="s">
+        <v>85</v>
+      </c>
+      <c r="K30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>150</v>
+      </c>
+      <c r="I31">
+        <v>150</v>
+      </c>
+      <c r="J31" t="s">
+        <v>85</v>
+      </c>
+      <c r="K31" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" t="s">
+        <v>106</v>
+      </c>
+      <c r="M31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>150</v>
+      </c>
+      <c r="I32">
+        <v>150</v>
+      </c>
+      <c r="J32" t="s">
+        <v>85</v>
+      </c>
+      <c r="K32" t="s">
+        <v>20</v>
+      </c>
+      <c r="L32" t="s">
+        <v>108</v>
+      </c>
+      <c r="M32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>60</v>
+      </c>
+      <c r="I33">
+        <v>60</v>
+      </c>
+      <c r="J33" t="s">
+        <v>85</v>
+      </c>
+      <c r="K33" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" t="s">
+        <v>110</v>
+      </c>
+      <c r="M33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>60</v>
+      </c>
+      <c r="I34">
+        <v>60</v>
+      </c>
+      <c r="J34" t="s">
+        <v>85</v>
+      </c>
+      <c r="K34" t="s">
+        <v>20</v>
+      </c>
+      <c r="L34" t="s">
+        <v>112</v>
+      </c>
+      <c r="M34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>60</v>
+      </c>
+      <c r="I35">
+        <v>60</v>
+      </c>
+      <c r="J35" t="s">
+        <v>85</v>
+      </c>
+      <c r="K35" t="s">
+        <v>20</v>
+      </c>
+      <c r="L35" t="s">
+        <v>114</v>
+      </c>
+      <c r="M35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" t="s">
+        <v>117</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>115</v>
+      </c>
+      <c r="I36">
+        <v>345</v>
+      </c>
+      <c r="J36" t="s">
+        <v>85</v>
+      </c>
+      <c r="K36" t="s">
+        <v>20</v>
+      </c>
+      <c r="L36" t="s">
+        <v>118</v>
+      </c>
+      <c r="M36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>60</v>
+      </c>
+      <c r="I37">
+        <v>60</v>
+      </c>
+      <c r="J37" t="s">
+        <v>85</v>
+      </c>
+      <c r="K37" t="s">
+        <v>20</v>
+      </c>
+      <c r="L37" t="s">
+        <v>120</v>
+      </c>
+      <c r="M37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>60</v>
+      </c>
+      <c r="I38">
+        <v>60</v>
+      </c>
+      <c r="J38" t="s">
+        <v>85</v>
+      </c>
+      <c r="K38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38" t="s">
+        <v>122</v>
+      </c>
+      <c r="M38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>50</v>
+      </c>
+      <c r="I39">
+        <v>50</v>
+      </c>
+      <c r="J39" t="s">
+        <v>85</v>
+      </c>
+      <c r="K39" t="s">
+        <v>20</v>
+      </c>
+      <c r="L39" t="s">
+        <v>125</v>
+      </c>
+      <c r="M39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>60</v>
+      </c>
+      <c r="I40">
+        <v>60</v>
+      </c>
+      <c r="J40" t="s">
+        <v>85</v>
+      </c>
+      <c r="K40" t="s">
+        <v>20</v>
+      </c>
+      <c r="L40" t="s">
+        <v>127</v>
+      </c>
+      <c r="M40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" t="s">
+        <v>55</v>
+      </c>
+      <c r="F41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>95</v>
+      </c>
+      <c r="I41">
+        <v>95</v>
+      </c>
+      <c r="J41" t="s">
+        <v>85</v>
+      </c>
+      <c r="K41" t="s">
+        <v>20</v>
+      </c>
+      <c r="L41" t="s">
+        <v>129</v>
+      </c>
+      <c r="M41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>130</v>
+      </c>
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>94</v>
+      </c>
+      <c r="I42">
+        <v>94</v>
+      </c>
+      <c r="J42" t="s">
+        <v>85</v>
+      </c>
+      <c r="K42" t="s">
+        <v>20</v>
+      </c>
+      <c r="L42" t="s">
+        <v>131</v>
+      </c>
+      <c r="M42" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>60</v>
+      </c>
+      <c r="I43">
+        <v>60</v>
+      </c>
+      <c r="J43" t="s">
+        <v>85</v>
+      </c>
+      <c r="K43" t="s">
+        <v>20</v>
+      </c>
+      <c r="L43" t="s">
+        <v>133</v>
+      </c>
+      <c r="M43" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>95</v>
+      </c>
+      <c r="I44">
+        <v>95</v>
+      </c>
+      <c r="J44" t="s">
+        <v>85</v>
+      </c>
+      <c r="K44" t="s">
+        <v>20</v>
+      </c>
+      <c r="L44" t="s">
+        <v>135</v>
+      </c>
+      <c r="M44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>50</v>
+      </c>
+      <c r="I45">
+        <v>50</v>
+      </c>
+      <c r="J45" t="s">
+        <v>85</v>
+      </c>
+      <c r="K45" t="s">
+        <v>20</v>
+      </c>
+      <c r="L45" t="s">
+        <v>137</v>
+      </c>
+      <c r="M45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" t="s">
+        <v>40</v>
+      </c>
+      <c r="E46" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" t="s">
+        <v>29</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>66</v>
+      </c>
+      <c r="I46">
+        <v>66</v>
+      </c>
+      <c r="J46" t="s">
+        <v>85</v>
+      </c>
+      <c r="K46" t="s">
+        <v>20</v>
+      </c>
+      <c r="L46" t="s">
+        <v>140</v>
+      </c>
+      <c r="M46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>94</v>
+      </c>
+      <c r="I47">
+        <v>94</v>
+      </c>
+      <c r="J47" t="s">
+        <v>85</v>
+      </c>
+      <c r="K47" t="s">
+        <v>20</v>
+      </c>
+      <c r="L47" t="s">
+        <v>142</v>
+      </c>
+      <c r="M47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>143</v>
+      </c>
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>94</v>
+      </c>
+      <c r="I48">
+        <v>94</v>
+      </c>
+      <c r="J48" t="s">
+        <v>85</v>
+      </c>
+      <c r="K48" t="s">
+        <v>20</v>
+      </c>
+      <c r="L48" t="s">
+        <v>144</v>
+      </c>
+      <c r="M48" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2100,39 +3187,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -2153,13 +3240,13 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2191,7 +3278,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2223,21 +3310,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2255,21 +3342,21 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2287,21 +3374,21 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2319,12 +3406,12 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2336,22 +3423,22 @@
         <v>40</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>1852</v>
+        <v>4590</v>
       </c>
       <c r="G8" t="s">
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2375,7 +3462,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -2384,24 +3471,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -2410,24 +3497,24 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>1350</v>
+        <v>1950</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -2436,293 +3523,293 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>720</v>
+        <v>1080</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>212</v>
+        <v>600</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>180</v>
+        <v>376</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>131</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
       <c r="F6">
-        <v>95</v>
+        <v>345</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>94</v>
+        <v>285</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8">
-        <v>88</v>
+        <v>212</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
         <v>60</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -2734,21 +3821,21 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2760,21 +3847,21 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>128</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2786,21 +3873,21 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2812,21 +3899,21 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2838,21 +3925,21 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>155</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2864,21 +3951,21 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2890,21 +3977,21 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="C21" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2916,21 +4003,21 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>128</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2942,21 +4029,21 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2968,21 +4055,21 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2994,21 +4081,21 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>169</v>
+        <v>216</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -3020,21 +4107,21 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -3046,21 +4133,21 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
       </c>
       <c r="D27">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -3072,21 +4159,21 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -3098,21 +4185,21 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -3124,21 +4211,21 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="B30" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -3150,21 +4237,21 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="B31" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -3176,15 +4263,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="B32" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3202,15 +4289,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="B33" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -3228,15 +4315,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="B34" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -3254,15 +4341,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="B35" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -3280,15 +4367,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -3306,15 +4393,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -3332,15 +4419,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="B38" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -3358,18 +4445,18 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="B39" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="C39" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="D39">
         <v>20</v>
@@ -3381,18 +4468,18 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="H39" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="B40" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="C40" t="s">
         <v>23</v>
@@ -3407,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="H40" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3421,7 +4508,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -3432,30 +4519,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -3478,7 +4565,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -3501,7 +4588,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -3524,7 +4611,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -3547,7 +4634,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -3570,7 +4657,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -3593,7 +4680,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -3612,6 +4699,29 @@
       </c>
       <c r="G8">
         <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9">
+        <v>2738</v>
+      </c>
+      <c r="C9">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9">
+        <v>119.04</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="271">
   <si>
     <t>Order ID</t>
   </si>
@@ -451,6 +451,21 @@
     <t>2026-05-04T22:10:40.162Z</t>
   </si>
   <si>
+    <t>ATH7817978342</t>
+  </si>
+  <si>
+    <t>2026-05-06T14:36:19.786Z</t>
+  </si>
+  <si>
+    <t>2026-05-06T14:39:38.351Z</t>
+  </si>
+  <si>
+    <t>ATH9038552316</t>
+  </si>
+  <si>
+    <t>2026-05-06T17:59:45.550Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -484,15 +499,15 @@
     <t>69df51939a28b213c15d5bfb</t>
   </si>
   <si>
-    <t>2026-04-28T12:17:31.160Z</t>
+    <t>2026-05-06T17:59:46.019Z</t>
+  </si>
+  <si>
+    <t>VIP</t>
   </si>
   <si>
     <t>Regular</t>
   </si>
   <si>
-    <t>VIP</t>
-  </si>
-  <si>
     <t>69d8d572ae6a1e8c2c032bc2</t>
   </si>
   <si>
@@ -550,16 +565,28 @@
     <t>69d8ef134922394efe9aeddf</t>
   </si>
   <si>
-    <t>Out of Stock</t>
+    <t>2026-05-06T15:21:31.177Z</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
   <si>
     <t>69d8ef144922394efe9aede2</t>
   </si>
   <si>
+    <t>2026-05-06T15:21:02.483Z</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
     <t>69d8ef134922394efe9aede0</t>
   </si>
   <si>
-    <t>Critical</t>
+    <t>2026-05-06T15:21:18.409Z</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
   <si>
     <t>69d8ef284922394efe9aee03</t>
@@ -571,21 +598,18 @@
     <t>69d8ef1d4922394efe9aedf1</t>
   </si>
   <si>
+    <t>2026-05-06T15:29:56.291Z</t>
+  </si>
+  <si>
     <t>69d8ef254922394efe9aedfe</t>
   </si>
   <si>
-    <t>Low</t>
-  </si>
-  <si>
     <t>69d8ef144922394efe9aede1</t>
   </si>
   <si>
     <t>69d8ef264922394efe9aee00</t>
   </si>
   <si>
-    <t>OK</t>
-  </si>
-  <si>
     <t>69d8ef174922394efe9aede7</t>
   </si>
   <si>
@@ -800,6 +824,9 @@
   </si>
   <si>
     <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -3153,7 +3180,7 @@
         <v>94</v>
       </c>
       <c r="J48" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K48" t="s">
         <v>20</v>
@@ -3162,6 +3189,88 @@
         <v>144</v>
       </c>
       <c r="M48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" t="s">
+        <v>124</v>
+      </c>
+      <c r="F49" t="s">
+        <v>60</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>50</v>
+      </c>
+      <c r="I49">
+        <v>50</v>
+      </c>
+      <c r="J49" t="s">
+        <v>41</v>
+      </c>
+      <c r="K49" t="s">
+        <v>20</v>
+      </c>
+      <c r="L49" t="s">
+        <v>146</v>
+      </c>
+      <c r="M49" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>148</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50">
+        <v>8</v>
+      </c>
+      <c r="H50">
+        <v>150</v>
+      </c>
+      <c r="I50">
+        <v>1200</v>
+      </c>
+      <c r="J50" t="s">
+        <v>85</v>
+      </c>
+      <c r="K50" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" t="s">
+        <v>149</v>
+      </c>
+      <c r="M50" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3187,39 +3296,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -3231,22 +3340,22 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>355</v>
+        <v>1645</v>
       </c>
       <c r="G2" t="s">
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -3278,7 +3387,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3310,21 +3419,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3342,21 +3451,21 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -3374,44 +3483,44 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
         <v>168</v>
-      </c>
-      <c r="D7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -3432,13 +3541,13 @@
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -3462,7 +3571,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -3471,24 +3580,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -3497,24 +3606,24 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>1950</v>
+        <v>3150</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="H2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -3523,7 +3632,7 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>9</v>
@@ -3532,15 +3641,15 @@
         <v>1080</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="H3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
@@ -3549,7 +3658,7 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -3558,15 +3667,15 @@
         <v>600</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>189</v>
       </c>
       <c r="H4" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -3587,12 +3696,12 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B6" t="s">
         <v>116</v>
@@ -3613,12 +3722,12 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -3627,7 +3736,7 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3636,15 +3745,15 @@
         <v>285</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
       <c r="H7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B8" t="s">
         <v>48</v>
@@ -3665,12 +3774,12 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" t="s">
         <v>124</v>
@@ -3679,24 +3788,24 @@
         <v>60</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
@@ -3717,12 +3826,12 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
@@ -3743,12 +3852,12 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
         <v>59</v>
@@ -3769,12 +3878,12 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
         <v>139</v>
@@ -3795,15 +3904,15 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -3821,15 +3930,15 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
@@ -3847,15 +3956,15 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C16" t="s">
         <v>60</v>
@@ -3873,15 +3982,15 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -3899,15 +4008,15 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
@@ -3925,15 +4034,15 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -3951,15 +4060,15 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -3977,15 +4086,15 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C21" t="s">
         <v>117</v>
@@ -4003,15 +4112,15 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C22" t="s">
         <v>117</v>
@@ -4029,15 +4138,15 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -4055,15 +4164,15 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
@@ -4081,15 +4190,15 @@
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C25" t="s">
         <v>26</v>
@@ -4107,15 +4216,15 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B26" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -4133,15 +4242,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B27" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -4159,15 +4268,15 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B28" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -4185,15 +4294,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -4211,15 +4320,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B30" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C30" t="s">
         <v>23</v>
@@ -4237,15 +4346,15 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B31" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C31" t="s">
         <v>60</v>
@@ -4263,15 +4372,15 @@
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B32" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -4289,15 +4398,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B33" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -4315,15 +4424,15 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B34" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -4341,15 +4450,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B35" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -4367,15 +4476,15 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B36" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -4393,15 +4502,15 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B37" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -4419,15 +4528,15 @@
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B38" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -4445,15 +4554,15 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C39" t="s">
         <v>117</v>
@@ -4468,18 +4577,18 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="H39" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B40" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C40" t="s">
         <v>23</v>
@@ -4494,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="H40" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -4508,7 +4617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -4519,30 +4628,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -4565,7 +4674,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -4588,7 +4697,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -4611,7 +4720,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -4634,7 +4743,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -4657,7 +4766,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -4680,7 +4789,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -4703,7 +4812,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B9">
         <v>2738</v>
@@ -4722,6 +4831,29 @@
       </c>
       <c r="G9">
         <v>119.04</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10">
+        <v>1290</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10">
+        <v>645</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="333">
   <si>
     <t>Order ID</t>
   </si>
@@ -466,6 +466,9 @@
     <t>2026-05-06T17:59:45.550Z</t>
   </si>
   <si>
+    <t>2026-05-06T18:01:45.395Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -574,24 +577,24 @@
     <t>69d8ef144922394efe9aede2</t>
   </si>
   <si>
-    <t>2026-05-06T15:21:02.483Z</t>
+    <t>2026-05-10T21:40:23.579Z</t>
+  </si>
+  <si>
+    <t>69d8ef134922394efe9aede0</t>
+  </si>
+  <si>
+    <t>2026-05-06T15:21:18.409Z</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>69d8ef284922394efe9aee03</t>
   </si>
   <si>
     <t>Critical</t>
   </si>
   <si>
-    <t>69d8ef134922394efe9aede0</t>
-  </si>
-  <si>
-    <t>2026-05-06T15:21:18.409Z</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>69d8ef284922394efe9aee03</t>
-  </si>
-  <si>
     <t>69d8ef1b4922394efe9aeded</t>
   </si>
   <si>
@@ -785,6 +788,189 @@
   </si>
   <si>
     <t>2026-05-04T13:21:20.906Z</t>
+  </si>
+  <si>
+    <t>69fe61604dfc5e28d4778a0d</t>
+  </si>
+  <si>
+    <t>Athar Midnight Heritage Tote</t>
+  </si>
+  <si>
+    <t>2026-05-08T22:19:11.313Z</t>
+  </si>
+  <si>
+    <t>69ff674c930f43fc7389752d</t>
+  </si>
+  <si>
+    <t>Athar Desert Sand Heritage Tote</t>
+  </si>
+  <si>
+    <t>2026-05-09T16:56:44.466Z</t>
+  </si>
+  <si>
+    <t>69ff827b61b6c73a91e2da68</t>
+  </si>
+  <si>
+    <t>Athar Midnight Heritage Hobo Bag</t>
+  </si>
+  <si>
+    <t>2026-05-09T18:52:43.570Z</t>
+  </si>
+  <si>
+    <t>69ff83cf61b6c73a91e2da6c</t>
+  </si>
+  <si>
+    <t>Athar Pearl Heritage Tote</t>
+  </si>
+  <si>
+    <t>2026-05-09T18:58:23.701Z</t>
+  </si>
+  <si>
+    <t>69ff852f61b6c73a91e2da71</t>
+  </si>
+  <si>
+    <t>Athar Earthly Heritage Bucket Bag</t>
+  </si>
+  <si>
+    <t>2026-05-09T19:04:14.801Z</t>
+  </si>
+  <si>
+    <t>69ff879861b6c73a91e2da75</t>
+  </si>
+  <si>
+    <t>Nablus Tote Bag</t>
+  </si>
+  <si>
+    <t>2026-05-09T19:14:32.698Z</t>
+  </si>
+  <si>
+    <t>69ff891861b6c73a91e2da7a</t>
+  </si>
+  <si>
+    <t>Athar Heritage Box Bag - Nablus Edition.</t>
+  </si>
+  <si>
+    <t>2026-05-09T19:20:55.822Z</t>
+  </si>
+  <si>
+    <t>69ff8a3f61b6c73a91e2da7e</t>
+  </si>
+  <si>
+    <t>Athar Olive Heritage Envelope Bag</t>
+  </si>
+  <si>
+    <t>2026-05-09T19:25:51.651Z</t>
+  </si>
+  <si>
+    <t>69ff8c0061b6c73a91e2da82</t>
+  </si>
+  <si>
+    <t>Title: Athar Burgundy Heritage Top Handle bag</t>
+  </si>
+  <si>
+    <t>2026-05-09T19:33:19.881Z</t>
+  </si>
+  <si>
+    <t>6a002e4bbd1dc81199f3c5f2</t>
+  </si>
+  <si>
+    <t>Athar Crimson Heritage Wallet</t>
+  </si>
+  <si>
+    <t>2026-05-10T07:05:47.340Z</t>
+  </si>
+  <si>
+    <t>6a002f37bd1dc81199f3c5f4</t>
+  </si>
+  <si>
+    <t>Athar Lavender Heritage Wallet</t>
+  </si>
+  <si>
+    <t>2026-05-10T07:09:43.713Z</t>
+  </si>
+  <si>
+    <t>6a002fe7bd1dc81199f3c5f6</t>
+  </si>
+  <si>
+    <t>Athar Olive Grove Wallet</t>
+  </si>
+  <si>
+    <t>2026-05-10T07:12:39.356Z</t>
+  </si>
+  <si>
+    <t>6a003bc8ae90c37e771e5014</t>
+  </si>
+  <si>
+    <t>Athar Slate Heritage Wallet</t>
+  </si>
+  <si>
+    <t>2026-05-10T08:03:20.059Z</t>
+  </si>
+  <si>
+    <t>6a003bc8ae90c37e771e5015</t>
+  </si>
+  <si>
+    <t>2026-05-10T08:03:20.316Z</t>
+  </si>
+  <si>
+    <t>6a003bcaae90c37e771e5017</t>
+  </si>
+  <si>
+    <t>2026-05-10T08:03:21.625Z</t>
+  </si>
+  <si>
+    <t>6a003cafae90c37e771e5019</t>
+  </si>
+  <si>
+    <t>Athar Golden Dome Heritage Watch</t>
+  </si>
+  <si>
+    <t>2026-05-10T08:07:10.984Z</t>
+  </si>
+  <si>
+    <t>6a003d4aae90c37e771e501b</t>
+  </si>
+  <si>
+    <t>Athar Tiberias Golden Mesh Watch</t>
+  </si>
+  <si>
+    <t>2026-05-10T08:09:46.205Z</t>
+  </si>
+  <si>
+    <t>6a003efdae90c37e771e501d</t>
+  </si>
+  <si>
+    <t>The Everlasting Bloom Motif.</t>
+  </si>
+  <si>
+    <t>2026-05-10T08:17:01.304Z</t>
+  </si>
+  <si>
+    <t>6a004120ae90c37e771e501f</t>
+  </si>
+  <si>
+    <t>Athar Jaffa Sunset Watch</t>
+  </si>
+  <si>
+    <t>2026-05-10T08:26:08.316Z</t>
+  </si>
+  <si>
+    <t>6a0041e5ae90c37e771e5021</t>
+  </si>
+  <si>
+    <t>Athar Bethlehem Dove of Peace Watch</t>
+  </si>
+  <si>
+    <t>2026-05-10T08:29:25.686Z</t>
+  </si>
+  <si>
+    <t>6a004302ae90c37e771e5023</t>
+  </si>
+  <si>
+    <t>Athar Ramallah Starry Horizon Watch</t>
+  </si>
+  <si>
+    <t>2026-05-10T08:34:10.136Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -3262,7 +3448,7 @@
         <v>1200</v>
       </c>
       <c r="J50" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="K50" t="s">
         <v>20</v>
@@ -3271,7 +3457,7 @@
         <v>149</v>
       </c>
       <c r="M50" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3296,39 +3482,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -3349,13 +3535,13 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -3387,7 +3573,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3419,21 +3605,21 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3451,54 +3637,54 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
         <v>169</v>
-      </c>
-      <c r="B6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" t="s">
         <v>172</v>
       </c>
-      <c r="B7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" t="s">
-        <v>171</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
@@ -3515,12 +3701,12 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -3541,13 +3727,13 @@
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3558,11 +3744,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
@@ -3571,7 +3757,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -3580,24 +3766,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -3606,7 +3792,7 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E2">
         <v>21</v>
@@ -3615,15 +3801,15 @@
         <v>3150</v>
       </c>
       <c r="G2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -3632,7 +3818,7 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>137</v>
       </c>
       <c r="E3">
         <v>9</v>
@@ -3641,10 +3827,10 @@
         <v>1080</v>
       </c>
       <c r="G3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3696,12 +3882,12 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B6" t="s">
         <v>116</v>
@@ -3722,12 +3908,12 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -3745,15 +3931,15 @@
         <v>285</v>
       </c>
       <c r="G7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B8" t="s">
         <v>48</v>
@@ -3779,7 +3965,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
         <v>124</v>
@@ -3805,7 +3991,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
@@ -3826,12 +4012,12 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
@@ -3852,12 +4038,12 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
         <v>59</v>
@@ -3883,7 +4069,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B13" t="s">
         <v>139</v>
@@ -3909,10 +4095,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -3935,10 +4121,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
@@ -3961,10 +4147,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C16" t="s">
         <v>60</v>
@@ -3987,10 +4173,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -4008,15 +4194,15 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
@@ -4039,10 +4225,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -4060,15 +4246,15 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -4091,10 +4277,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C21" t="s">
         <v>117</v>
@@ -4117,10 +4303,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" t="s">
         <v>117</v>
@@ -4143,10 +4329,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -4169,10 +4355,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
@@ -4195,10 +4381,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C25" t="s">
         <v>26</v>
@@ -4221,10 +4407,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -4242,15 +4428,15 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B27" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -4273,10 +4459,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B28" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -4294,15 +4480,15 @@
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -4320,15 +4506,15 @@
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C30" t="s">
         <v>23</v>
@@ -4351,10 +4537,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C31" t="s">
         <v>60</v>
@@ -4377,10 +4563,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B32" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -4398,15 +4584,15 @@
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B33" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
@@ -4429,10 +4615,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
@@ -4450,15 +4636,15 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B35" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C35" t="s">
         <v>60</v>
@@ -4481,10 +4667,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B36" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -4507,10 +4693,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
@@ -4533,10 +4719,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B38" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -4554,15 +4740,15 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B39" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C39" t="s">
         <v>117</v>
@@ -4577,18 +4763,18 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H39" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B40" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C40" t="s">
         <v>23</v>
@@ -4603,10 +4789,556 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H40" t="s">
-        <v>184</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>258</v>
+      </c>
+      <c r="B41" t="s">
+        <v>259</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41">
+        <v>10</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
+        <v>260</v>
+      </c>
+      <c r="H41" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>261</v>
+      </c>
+      <c r="B42" t="s">
+        <v>262</v>
+      </c>
+      <c r="C42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42" t="s">
+        <v>263</v>
+      </c>
+      <c r="H42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>264</v>
+      </c>
+      <c r="B43" t="s">
+        <v>265</v>
+      </c>
+      <c r="C43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" t="s">
+        <v>266</v>
+      </c>
+      <c r="H43" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>267</v>
+      </c>
+      <c r="B44" t="s">
+        <v>268</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44" t="s">
+        <v>269</v>
+      </c>
+      <c r="H44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>270</v>
+      </c>
+      <c r="B45" t="s">
+        <v>271</v>
+      </c>
+      <c r="C45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45">
+        <v>10</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>272</v>
+      </c>
+      <c r="H45" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>273</v>
+      </c>
+      <c r="B46" t="s">
+        <v>274</v>
+      </c>
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>275</v>
+      </c>
+      <c r="H46" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>276</v>
+      </c>
+      <c r="B47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C47" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
+        <v>278</v>
+      </c>
+      <c r="H47" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>279</v>
+      </c>
+      <c r="B48" t="s">
+        <v>280</v>
+      </c>
+      <c r="C48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48" t="s">
+        <v>281</v>
+      </c>
+      <c r="H48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>282</v>
+      </c>
+      <c r="B49" t="s">
+        <v>283</v>
+      </c>
+      <c r="C49" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49">
+        <v>10</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>284</v>
+      </c>
+      <c r="H49" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>285</v>
+      </c>
+      <c r="B50" t="s">
+        <v>286</v>
+      </c>
+      <c r="C50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50">
+        <v>10</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>287</v>
+      </c>
+      <c r="H50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>288</v>
+      </c>
+      <c r="B51" t="s">
+        <v>289</v>
+      </c>
+      <c r="C51" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51">
+        <v>10</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
+        <v>290</v>
+      </c>
+      <c r="H51" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>291</v>
+      </c>
+      <c r="B52" t="s">
+        <v>292</v>
+      </c>
+      <c r="C52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52" t="s">
+        <v>293</v>
+      </c>
+      <c r="H52" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>294</v>
+      </c>
+      <c r="B53" t="s">
+        <v>295</v>
+      </c>
+      <c r="C53" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53">
+        <v>10</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53" t="s">
+        <v>296</v>
+      </c>
+      <c r="H53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>297</v>
+      </c>
+      <c r="B54" t="s">
+        <v>295</v>
+      </c>
+      <c r="C54" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54">
+        <v>10</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>298</v>
+      </c>
+      <c r="H54" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>299</v>
+      </c>
+      <c r="B55" t="s">
+        <v>295</v>
+      </c>
+      <c r="C55" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
+        <v>300</v>
+      </c>
+      <c r="H55" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>301</v>
+      </c>
+      <c r="B56" t="s">
+        <v>302</v>
+      </c>
+      <c r="C56" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56">
+        <v>10</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
+        <v>303</v>
+      </c>
+      <c r="H56" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>304</v>
+      </c>
+      <c r="B57" t="s">
+        <v>305</v>
+      </c>
+      <c r="C57" t="s">
+        <v>117</v>
+      </c>
+      <c r="D57">
+        <v>10</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57" t="s">
+        <v>306</v>
+      </c>
+      <c r="H57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>307</v>
+      </c>
+      <c r="B58" t="s">
+        <v>308</v>
+      </c>
+      <c r="C58" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58">
+        <v>10</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
+        <v>309</v>
+      </c>
+      <c r="H58" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>310</v>
+      </c>
+      <c r="B59" t="s">
+        <v>311</v>
+      </c>
+      <c r="C59" t="s">
+        <v>117</v>
+      </c>
+      <c r="D59">
+        <v>10</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
+        <v>312</v>
+      </c>
+      <c r="H59" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>313</v>
+      </c>
+      <c r="B60" t="s">
+        <v>314</v>
+      </c>
+      <c r="C60" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60">
+        <v>10</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>315</v>
+      </c>
+      <c r="H60" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>316</v>
+      </c>
+      <c r="B61" t="s">
+        <v>317</v>
+      </c>
+      <c r="C61" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61">
+        <v>10</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>318</v>
+      </c>
+      <c r="H61" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -4628,30 +5360,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>320</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>259</v>
+        <v>321</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>260</v>
+        <v>322</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>261</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -4674,7 +5406,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -4697,7 +5429,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -4720,7 +5452,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -4743,7 +5475,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>266</v>
+        <v>328</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -4766,7 +5498,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>267</v>
+        <v>329</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -4789,7 +5521,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>268</v>
+        <v>330</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -4812,7 +5544,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>269</v>
+        <v>331</v>
       </c>
       <c r="B9">
         <v>2738</v>
@@ -4835,7 +5567,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>332</v>
       </c>
       <c r="B10">
         <v>1290</v>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="480">
   <si>
     <t>Order ID</t>
   </si>
@@ -55,33 +55,123 @@
     <t>Delivery Date</t>
   </si>
   <si>
+    <t>ATH5355779279</t>
+  </si>
+  <si>
+    <t>Abdalhadi Raed Abdalhadi Shelbaya</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0595179951</t>
+  </si>
+  <si>
+    <t>Peacock Eye Wallet</t>
+  </si>
+  <si>
+    <t>Wallets</t>
+  </si>
+  <si>
+    <t>Delivered</t>
+  </si>
+  <si>
+    <t>Cash on Delivery</t>
+  </si>
+  <si>
+    <t>2026-04-10T12:57:18.177Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:19:22.305Z</t>
+  </si>
+  <si>
+    <t>ATH5355763545</t>
+  </si>
+  <si>
+    <t>2026-04-10T13:10:58.380Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:19:46.881Z</t>
+  </si>
+  <si>
+    <t>ATH5355747776</t>
+  </si>
+  <si>
+    <t>2026-04-10T13:18:12.866Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:20:14.114Z</t>
+  </si>
+  <si>
+    <t>Bethlehem Star Bracelet</t>
+  </si>
+  <si>
+    <t>Bracelets</t>
+  </si>
+  <si>
+    <t>ATH5355731357</t>
+  </si>
+  <si>
+    <t>2026-04-10T13:19:10.609Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:20:40.228Z</t>
+  </si>
+  <si>
+    <t>273759770</t>
+  </si>
+  <si>
+    <t>2026-04-10T13:29:05.453Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:21:04.495Z</t>
+  </si>
+  <si>
+    <t>273759740</t>
+  </si>
+  <si>
+    <t>Athar Gaza Rose Handbag</t>
+  </si>
+  <si>
+    <t>Bags</t>
+  </si>
+  <si>
+    <t>2026-04-10T13:30:39.423Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:21:43.007Z</t>
+  </si>
+  <si>
+    <t>273759368</t>
+  </si>
+  <si>
+    <t>2026-04-10T13:38:26.905Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:22:09.208Z</t>
+  </si>
+  <si>
+    <t>273759230</t>
+  </si>
+  <si>
+    <t>2026-04-10T13:40:30.487Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:24:26.740Z</t>
+  </si>
+  <si>
     <t>228461655</t>
   </si>
   <si>
     <t>abood shel</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>0595179951</t>
-  </si>
-  <si>
-    <t>Athar Gaza Rose Handbag</t>
-  </si>
-  <si>
-    <t>Bags</t>
-  </si>
-  <si>
-    <t>Shipped</t>
-  </si>
-  <si>
-    <t>Cash on Delivery</t>
-  </si>
-  <si>
     <t>2026-04-10T13:52:59.392Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:24:39.273Z</t>
+  </si>
+  <si>
     <t>Mashrabiya Square Jewelry Set</t>
   </si>
   <si>
@@ -91,19 +181,10 @@
     <t>225387152</t>
   </si>
   <si>
-    <t>Peacock Eye Wallet</t>
-  </si>
-  <si>
-    <t>Wallets</t>
-  </si>
-  <si>
     <t>2026-04-10T14:10:25.647Z</t>
   </si>
   <si>
-    <t>Bethlehem Star Bracelet</t>
-  </si>
-  <si>
-    <t>Bracelets</t>
+    <t>2026-05-11T10:24:55.624Z</t>
   </si>
   <si>
     <t>ATH0624030283</t>
@@ -115,18 +196,27 @@
     <t>2026-04-11T11:17:20.309Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:25:08.417Z</t>
+  </si>
+  <si>
     <t>ATH2793666663</t>
   </si>
   <si>
     <t>2026-04-11T17:18:56.695Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:25:22.056Z</t>
+  </si>
+  <si>
     <t>ATH3812682239</t>
   </si>
   <si>
     <t>2026-04-11T20:08:46.838Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:25:37.012Z</t>
+  </si>
+  <si>
     <t>ATH4821265794</t>
   </si>
   <si>
@@ -139,9 +229,6 @@
     <t>+970595638731</t>
   </si>
   <si>
-    <t>Delivered</t>
-  </si>
-  <si>
     <t>2026-04-15T10:16:52.660Z</t>
   </si>
   <si>
@@ -259,6 +346,15 @@
     <t>Coastal Card Holder</t>
   </si>
   <si>
+    <t>ATH6498524341</t>
+  </si>
+  <si>
+    <t>2026-04-16T18:43:05.251Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:26:08.730Z</t>
+  </si>
+  <si>
     <t>ATH5452644412</t>
   </si>
   <si>
@@ -268,15 +364,27 @@
     <t>2026-04-17T19:37:57.927Z</t>
   </si>
   <si>
+    <t>ATH7767835879</t>
+  </si>
+  <si>
+    <t>Sunburst Cuff Bangle</t>
+  </si>
+  <si>
+    <t>2026-04-28T12:01:18.377Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:26:40.172Z</t>
+  </si>
+  <si>
     <t>ATH7818942656</t>
   </si>
   <si>
-    <t>Confirmed</t>
-  </si>
-  <si>
     <t>2026-04-28T12:09:49.429Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:27:09.969Z</t>
+  </si>
+  <si>
     <t>ATH4702950114</t>
   </si>
   <si>
@@ -301,66 +409,99 @@
     <t>2026-05-03T19:34:17.398Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:27:34.040Z</t>
+  </si>
+  <si>
     <t>ATH0702914363</t>
   </si>
   <si>
     <t>2026-05-04T15:03:49.150Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:27:54.832Z</t>
+  </si>
+  <si>
     <t>ATH0703618564</t>
   </si>
   <si>
     <t>2026-05-04T15:03:56.186Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:28:16.020Z</t>
+  </si>
+  <si>
     <t>ATH0707085075</t>
   </si>
   <si>
     <t>2026-05-04T15:04:30.851Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:28:37.708Z</t>
+  </si>
+  <si>
     <t>ATH0712002761</t>
   </si>
   <si>
     <t>2026-05-04T15:05:20.028Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:33:17.480Z</t>
+  </si>
+  <si>
     <t>ATH0715077389</t>
   </si>
   <si>
     <t>2026-05-04T15:05:50.774Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:32:57.105Z</t>
+  </si>
+  <si>
     <t>ATH1908441937</t>
   </si>
   <si>
     <t>2026-05-04T18:24:44.427Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:32:37.132Z</t>
+  </si>
+  <si>
     <t>ATH1908966379</t>
   </si>
   <si>
     <t>2026-05-04T18:24:49.664Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:32:18.808Z</t>
+  </si>
+  <si>
     <t>ATH1912135035</t>
   </si>
   <si>
     <t>2026-05-04T18:25:21.352Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:32:02.008Z</t>
+  </si>
+  <si>
     <t>ATH1926037538</t>
   </si>
   <si>
     <t>2026-05-04T18:27:40.376Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:31:42.969Z</t>
+  </si>
+  <si>
     <t>ATH1931228735</t>
   </si>
   <si>
     <t>2026-05-04T18:28:32.295Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:31:22.289Z</t>
+  </si>
+  <si>
     <t>ATH1937654837</t>
   </si>
   <si>
@@ -373,18 +514,27 @@
     <t>2026-05-04T18:29:36.549Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:31:02.407Z</t>
+  </si>
+  <si>
     <t>ATH2041136067</t>
   </si>
   <si>
     <t>2026-05-04T18:46:51.361Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:30:43.371Z</t>
+  </si>
+  <si>
     <t>ATH2044885659</t>
   </si>
   <si>
     <t>2026-05-04T18:47:28.858Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:30:25.849Z</t>
+  </si>
+  <si>
     <t>ATH2048541897</t>
   </si>
   <si>
@@ -394,42 +544,63 @@
     <t>2026-05-04T18:48:05.421Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:30:07.835Z</t>
+  </si>
+  <si>
     <t>ATH2596159649</t>
   </si>
   <si>
     <t>2026-05-04T20:19:21.602Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:18:46.154Z</t>
+  </si>
+  <si>
     <t>ATH2636230029</t>
   </si>
   <si>
     <t>2026-05-04T20:26:02.307Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:19:00.694Z</t>
+  </si>
+  <si>
     <t>ATH2683918667</t>
   </si>
   <si>
     <t>2026-05-04T20:33:59.194Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:17:24.585Z</t>
+  </si>
+  <si>
     <t>ATH2390836574</t>
   </si>
   <si>
     <t>2026-05-04T19:45:08.372Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:29:48.685Z</t>
+  </si>
+  <si>
     <t>ATH2403975287</t>
   </si>
   <si>
     <t>2026-05-04T19:47:19.754Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:29:33.011Z</t>
+  </si>
+  <si>
     <t>ATH2770081328</t>
   </si>
   <si>
     <t>2026-05-04T20:48:20.815Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:18:25.982Z</t>
+  </si>
+  <si>
     <t>ATH2416012187</t>
   </si>
   <si>
@@ -439,18 +610,27 @@
     <t>2026-05-04T19:49:20.123Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:29:12.640Z</t>
+  </si>
+  <si>
     <t>ATH2436239317</t>
   </si>
   <si>
     <t>2026-05-04T19:52:42.395Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:28:55.128Z</t>
+  </si>
+  <si>
     <t>ATH3264015680</t>
   </si>
   <si>
     <t>2026-05-04T22:10:40.162Z</t>
   </si>
   <si>
+    <t>2026-05-11T10:18:34.381Z</t>
+  </si>
+  <si>
     <t>ATH7817978342</t>
   </si>
   <si>
@@ -469,6 +649,153 @@
     <t>2026-05-06T18:01:45.395Z</t>
   </si>
   <si>
+    <t>ATH9717990835</t>
+  </si>
+  <si>
+    <t>shahd sorakji</t>
+  </si>
+  <si>
+    <t>shahdsorakji0@gmail.com</t>
+  </si>
+  <si>
+    <t>+970594896951</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:59:39.914Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:05:13.403Z</t>
+  </si>
+  <si>
+    <t>Athar Ramallah Starry Horizon Watch</t>
+  </si>
+  <si>
+    <t>Athar Bethlehem Dove of Peace Watch</t>
+  </si>
+  <si>
+    <t>ATH9731641627</t>
+  </si>
+  <si>
+    <t>Athar Jaffa Sunset Watch</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:01:56.420Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:05:35.969Z</t>
+  </si>
+  <si>
+    <t>Athar Golden Radiance Watch</t>
+  </si>
+  <si>
+    <t>Athar Golden Dome Heritage Watch</t>
+  </si>
+  <si>
+    <t>The Everlasting Bloom Motif.</t>
+  </si>
+  <si>
+    <t>ATH9850556836</t>
+  </si>
+  <si>
+    <t>kareema aboshqdam</t>
+  </si>
+  <si>
+    <t>kareemaaboshqdam@gmail.com</t>
+  </si>
+  <si>
+    <t>+970593696717</t>
+  </si>
+  <si>
+    <t>Nablus Tote Bag</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:21:45.572Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:20:23.044Z</t>
+  </si>
+  <si>
+    <t>ATH9861928698</t>
+  </si>
+  <si>
+    <t>Grapevine Shoulder Bag</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:23:39.288Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:20:33.934Z</t>
+  </si>
+  <si>
+    <t>ATH9886892039</t>
+  </si>
+  <si>
+    <t>darin halaweh</t>
+  </si>
+  <si>
+    <t>darinhalaweh2006@gmail.com</t>
+  </si>
+  <si>
+    <t>+970595731827</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:27:48.923Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:20:13.258Z</t>
+  </si>
+  <si>
+    <t>Athar Heritage Box Bag - Nablus Edition.</t>
+  </si>
+  <si>
+    <t>Title: Athar Burgundy Heritage Top Handle bag</t>
+  </si>
+  <si>
+    <t>Athar Midnight Heritage Hobo Bag</t>
+  </si>
+  <si>
+    <t>Athar Pearl Heritage Tote</t>
+  </si>
+  <si>
+    <t>ATH9949799244</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:38:17.996Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:19:45.764Z</t>
+  </si>
+  <si>
+    <t>ATH0014828261</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:49:08.286Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:18:32.025Z</t>
+  </si>
+  <si>
+    <t>Athar Slate Heritage Wallet</t>
+  </si>
+  <si>
+    <t>ATH1260446548</t>
+  </si>
+  <si>
+    <t>Delivery</t>
+  </si>
+  <si>
+    <t>delivery@athar.com</t>
+  </si>
+  <si>
+    <t>+970000000000</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:16:44.487Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:18:07.976Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -499,18 +826,69 @@
     <t>Customer Segment</t>
   </si>
   <si>
+    <t>2026-05-11T10:26:28.715Z</t>
+  </si>
+  <si>
+    <t>VIP</t>
+  </si>
+  <si>
     <t>69df51939a28b213c15d5bfb</t>
   </si>
   <si>
     <t>2026-05-06T17:59:46.019Z</t>
   </si>
   <si>
-    <t>VIP</t>
+    <t>6a01bbfa695111dcf9655902</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:27:49.601Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:49:08.973Z</t>
+  </si>
+  <si>
+    <t>69fb511c773f2b0f7ec3b81f</t>
+  </si>
+  <si>
+    <t>2026-05-11T15:16:45.171Z</t>
+  </si>
+  <si>
+    <t>6a01ba79695111dcf96558e5</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:21:46.268Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:23:39.976Z</t>
   </si>
   <si>
     <t>Regular</t>
   </si>
   <si>
+    <t>6a01b546695111dcf96558a5</t>
+  </si>
+  <si>
+    <t>2026-05-11T10:59:40.595Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T11:01:57.108Z</t>
+  </si>
+  <si>
+    <t>6a02065d695111dcf9655df7</t>
+  </si>
+  <si>
+    <t>𝚂𝚑𝚘𝚛𝚘𝚚</t>
+  </si>
+  <si>
+    <t>shoroqfoqha21@gmail.com</t>
+  </si>
+  <si>
+    <t>+970592434550</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
     <t>69d8d572ae6a1e8c2c032bc2</t>
   </si>
   <si>
@@ -523,9 +901,6 @@
     <t>0599999999</t>
   </si>
   <si>
-    <t>New</t>
-  </si>
-  <si>
     <t>69da482fe63ef65d62c51026</t>
   </si>
   <si>
@@ -541,10 +916,22 @@
     <t>your-email@example.com</t>
   </si>
   <si>
+    <t>6a01c01b695111dcf965593c</t>
+  </si>
+  <si>
+    <t>wafaa snober</t>
+  </si>
+  <si>
+    <t>wafaasnober48@gmail.com</t>
+  </si>
+  <si>
+    <t>+970598717719</t>
+  </si>
+  <si>
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
-    <t>2026-05-04T22:10:41.075Z</t>
+    <t>2026-05-11T10:25:59.379Z</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -568,7 +955,7 @@
     <t>69d8ef134922394efe9aeddf</t>
   </si>
   <si>
-    <t>2026-05-06T15:21:31.177Z</t>
+    <t>2026-05-11T07:25:33.206Z</t>
   </si>
   <si>
     <t>OK</t>
@@ -577,115 +964,241 @@
     <t>69d8ef144922394efe9aede2</t>
   </si>
   <si>
-    <t>2026-05-10T21:40:23.579Z</t>
+    <t>2026-05-11T07:26:24.358Z</t>
   </si>
   <si>
     <t>69d8ef134922394efe9aede0</t>
   </si>
   <si>
-    <t>2026-05-06T15:21:18.409Z</t>
-  </si>
-  <si>
-    <t>Low</t>
+    <t>2026-05-11T07:26:00.153Z</t>
+  </si>
+  <si>
+    <t>69d8ef224922394efe9aedf9</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:26:14.886Z</t>
+  </si>
+  <si>
+    <t>69d8ef1b4922394efe9aeded</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:26:21.822Z</t>
   </si>
   <si>
     <t>69d8ef284922394efe9aee03</t>
   </si>
   <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>69d8ef1b4922394efe9aeded</t>
+    <t>2026-05-11T07:26:18.672Z</t>
   </si>
   <si>
     <t>69d8ef1d4922394efe9aedf1</t>
   </si>
   <si>
-    <t>2026-05-06T15:29:56.291Z</t>
+    <t>2026-05-11T07:26:16.640Z</t>
+  </si>
+  <si>
+    <t>69d8ef254922394efe9aedff</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:26:26.082Z</t>
+  </si>
+  <si>
+    <t>69d8ef144922394efe9aede1</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:26:07.307Z</t>
   </si>
   <si>
     <t>69d8ef254922394efe9aedfe</t>
   </si>
   <si>
-    <t>69d8ef144922394efe9aede1</t>
+    <t>2026-05-11T07:26:27.694Z</t>
+  </si>
+  <si>
+    <t>69f20e78c49efb1805c2fc83</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:35.352Z</t>
+  </si>
+  <si>
+    <t>6a003cafae90c37e771e5019</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:34.378Z</t>
+  </si>
+  <si>
+    <t>6a003efdae90c37e771e501d</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:26:31.292Z</t>
+  </si>
+  <si>
+    <t>6a004120ae90c37e771e501f</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:39.824Z</t>
+  </si>
+  <si>
+    <t>6a0041e5ae90c37e771e5021</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:30.214Z</t>
+  </si>
+  <si>
+    <t>6a004302ae90c37e771e5023</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:51.249Z</t>
   </si>
   <si>
     <t>69d8ef264922394efe9aee00</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:28.602Z</t>
+  </si>
+  <si>
+    <t>69ff891861b6c73a91e2da7a</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:36.450Z</t>
+  </si>
+  <si>
+    <t>69ff8c0061b6c73a91e2da82</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:26:32.294Z</t>
+  </si>
+  <si>
     <t>69d8ef174922394efe9aede7</t>
   </si>
   <si>
-    <t>69d8ef254922394efe9aedff</t>
+    <t>2026-05-11T07:26:04.959Z</t>
   </si>
   <si>
     <t>69d8ef214922394efe9aedf8</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:10.377Z</t>
+  </si>
+  <si>
+    <t>69d8ef1c4922394efe9aedef</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:26:30.106Z</t>
+  </si>
+  <si>
+    <t>69ff827b61b6c73a91e2da68</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:41.399Z</t>
+  </si>
+  <si>
+    <t>69ff83cf61b6c73a91e2da6c</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:47.570Z</t>
+  </si>
+  <si>
+    <t>69ff879861b6c73a91e2da75</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:26:21.197Z</t>
+  </si>
+  <si>
+    <t>6a003bc8ae90c37e771e5015</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:57.632Z</t>
+  </si>
+  <si>
     <t>69d8ef154922394efe9aede3</t>
   </si>
   <si>
     <t>Geometric Diamond Sunglasses</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:11.742Z</t>
+  </si>
+  <si>
     <t>69d8ef164922394efe9aede4</t>
   </si>
   <si>
     <t>Wave Belt Bracelet</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:33.214Z</t>
+  </si>
+  <si>
     <t>69d8ef164922394efe9aede5</t>
   </si>
   <si>
     <t>Palestinian Geometric Engraving</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:23.706Z</t>
+  </si>
+  <si>
     <t>69d8ef174922394efe9aede6</t>
   </si>
   <si>
     <t>Wheat Ear Set</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:34.540Z</t>
+  </si>
+  <si>
     <t>69d8ef184922394efe9aede8</t>
   </si>
   <si>
     <t>Desert Carryall</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:06.330Z</t>
+  </si>
+  <si>
     <t>69d8ef194922394efe9aede9</t>
   </si>
   <si>
     <t>Olive Crest Key Charm</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:22.463Z</t>
+  </si>
+  <si>
     <t>69d8ef194922394efe9aedea</t>
   </si>
   <si>
     <t>Mosaic Sun Medallion</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:20.574Z</t>
+  </si>
+  <si>
     <t>69d8ef1a4922394efe9aedeb</t>
   </si>
   <si>
     <t>Citrus Orchard Watch</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:03.985Z</t>
+  </si>
+  <si>
     <t>69d8ef1b4922394efe9aedec</t>
   </si>
   <si>
     <t>Cedar Bloom Watch</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:03.212Z</t>
+  </si>
+  <si>
     <t>69d8ef1c4922394efe9aedee</t>
   </si>
   <si>
     <t>Floral Hand Chain</t>
   </si>
   <si>
-    <t>69d8ef1c4922394efe9aedef</t>
-  </si>
-  <si>
-    <t>Sunburst Cuff Bangle</t>
+    <t>2026-05-11T07:26:09.456Z</t>
   </si>
   <si>
     <t>69d8ef1d4922394efe9aedf0</t>
@@ -694,46 +1207,61 @@
     <t>Bethlehem Star Card Sleeve</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:01.078Z</t>
+  </si>
+  <si>
     <t>69d8ef1e4922394efe9aedf2</t>
   </si>
   <si>
     <t>Leaf Crest Key Charm</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:17.994Z</t>
+  </si>
+  <si>
     <t>69d8ef1e4922394efe9aedf3</t>
   </si>
   <si>
     <t>Script Medallion Pendant</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:26.842Z</t>
+  </si>
+  <si>
     <t>69d8ef1f4922394efe9aedf4</t>
   </si>
   <si>
     <t>Mosaic Diamond Necklace</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:19.950Z</t>
+  </si>
+  <si>
     <t>69d8ef204922394efe9aedf5</t>
   </si>
   <si>
     <t>Heritage Bookmark Charm</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:15.921Z</t>
+  </si>
+  <si>
     <t>69d8ef204922394efe9aedf6</t>
   </si>
   <si>
     <t>Blossom Column Set</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:02.102Z</t>
+  </si>
+  <si>
     <t>69d8ef214922394efe9aedf7</t>
   </si>
   <si>
     <t>Grape Motif Ring Set</t>
   </si>
   <si>
-    <t>69d8ef224922394efe9aedf9</t>
-  </si>
-  <si>
-    <t>Grapevine Shoulder Bag</t>
+    <t>2026-05-11T07:26:12.773Z</t>
   </si>
   <si>
     <t>69d8ef224922394efe9aedfa</t>
@@ -742,43 +1270,52 @@
     <t>Sunburst Bloom Bracelet</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:29.457Z</t>
+  </si>
+  <si>
     <t>69d8ef234922394efe9aedfb</t>
   </si>
   <si>
     <t>Petal Vine Bracelet</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:25.035Z</t>
+  </si>
+  <si>
     <t>69d8ef244922394efe9aedfc</t>
   </si>
   <si>
     <t>Lattice Wrap Ring</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:17.355Z</t>
+  </si>
+  <si>
     <t>69d8ef244922394efe9aedfd</t>
   </si>
   <si>
     <t>Filigree Round Sunglasses</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:08.460Z</t>
+  </si>
+  <si>
     <t>69d8ef274922394efe9aee01</t>
   </si>
   <si>
     <t>Midnight Zip Card Wallet</t>
   </si>
   <si>
+    <t>2026-05-11T07:26:19.307Z</t>
+  </si>
+  <si>
     <t>69d8ef274922394efe9aee02</t>
   </si>
   <si>
     <t>Olive Square Jewelry Set</t>
   </si>
   <si>
-    <t>69f20e78c49efb1805c2fc83</t>
-  </si>
-  <si>
-    <t>Athar Golden Radiance Watch</t>
-  </si>
-  <si>
-    <t>2026-04-29T13:58:16.464Z</t>
+    <t>2026-05-11T07:26:23.085Z</t>
   </si>
   <si>
     <t>69f89d51987705d82e7eeaef</t>
@@ -787,7 +1324,7 @@
     <t>roro</t>
   </si>
   <si>
-    <t>2026-05-04T13:21:20.906Z</t>
+    <t>2026-05-11T07:26:35.323Z</t>
   </si>
   <si>
     <t>69fe61604dfc5e28d4778a0d</t>
@@ -796,7 +1333,7 @@
     <t>Athar Midnight Heritage Tote</t>
   </si>
   <si>
-    <t>2026-05-08T22:19:11.313Z</t>
+    <t>2026-05-11T07:25:42.190Z</t>
   </si>
   <si>
     <t>69ff674c930f43fc7389752d</t>
@@ -805,25 +1342,7 @@
     <t>Athar Desert Sand Heritage Tote</t>
   </si>
   <si>
-    <t>2026-05-09T16:56:44.466Z</t>
-  </si>
-  <si>
-    <t>69ff827b61b6c73a91e2da68</t>
-  </si>
-  <si>
-    <t>Athar Midnight Heritage Hobo Bag</t>
-  </si>
-  <si>
-    <t>2026-05-09T18:52:43.570Z</t>
-  </si>
-  <si>
-    <t>69ff83cf61b6c73a91e2da6c</t>
-  </si>
-  <si>
-    <t>Athar Pearl Heritage Tote</t>
-  </si>
-  <si>
-    <t>2026-05-09T18:58:23.701Z</t>
+    <t>2026-05-11T07:25:31.505Z</t>
   </si>
   <si>
     <t>69ff852f61b6c73a91e2da71</t>
@@ -832,25 +1351,7 @@
     <t>Athar Earthly Heritage Bucket Bag</t>
   </si>
   <si>
-    <t>2026-05-09T19:04:14.801Z</t>
-  </si>
-  <si>
-    <t>69ff879861b6c73a91e2da75</t>
-  </si>
-  <si>
-    <t>Nablus Tote Bag</t>
-  </si>
-  <si>
-    <t>2026-05-09T19:14:32.698Z</t>
-  </si>
-  <si>
-    <t>69ff891861b6c73a91e2da7a</t>
-  </si>
-  <si>
-    <t>Athar Heritage Box Bag - Nablus Edition.</t>
-  </si>
-  <si>
-    <t>2026-05-09T19:20:55.822Z</t>
+    <t>2026-05-11T07:25:32.191Z</t>
   </si>
   <si>
     <t>69ff8a3f61b6c73a91e2da7e</t>
@@ -859,16 +1360,7 @@
     <t>Athar Olive Heritage Envelope Bag</t>
   </si>
   <si>
-    <t>2026-05-09T19:25:51.651Z</t>
-  </si>
-  <si>
-    <t>69ff8c0061b6c73a91e2da82</t>
-  </si>
-  <si>
-    <t>Title: Athar Burgundy Heritage Top Handle bag</t>
-  </si>
-  <si>
-    <t>2026-05-09T19:33:19.881Z</t>
+    <t>2026-05-11T07:25:45.009Z</t>
   </si>
   <si>
     <t>6a002e4bbd1dc81199f3c5f2</t>
@@ -877,7 +1369,7 @@
     <t>Athar Crimson Heritage Wallet</t>
   </si>
   <si>
-    <t>2026-05-10T07:05:47.340Z</t>
+    <t>2026-05-11T07:25:30.856Z</t>
   </si>
   <si>
     <t>6a002f37bd1dc81199f3c5f4</t>
@@ -886,7 +1378,7 @@
     <t>Athar Lavender Heritage Wallet</t>
   </si>
   <si>
-    <t>2026-05-10T07:09:43.713Z</t>
+    <t>2026-05-11T07:25:40.621Z</t>
   </si>
   <si>
     <t>6a002fe7bd1dc81199f3c5f6</t>
@@ -895,37 +1387,19 @@
     <t>Athar Olive Grove Wallet</t>
   </si>
   <si>
-    <t>2026-05-10T07:12:39.356Z</t>
+    <t>2026-05-11T07:25:43.448Z</t>
   </si>
   <si>
     <t>6a003bc8ae90c37e771e5014</t>
   </si>
   <si>
-    <t>Athar Slate Heritage Wallet</t>
-  </si>
-  <si>
-    <t>2026-05-10T08:03:20.059Z</t>
-  </si>
-  <si>
-    <t>6a003bc8ae90c37e771e5015</t>
-  </si>
-  <si>
-    <t>2026-05-10T08:03:20.316Z</t>
+    <t>2026-05-11T07:25:58.557Z</t>
   </si>
   <si>
     <t>6a003bcaae90c37e771e5017</t>
   </si>
   <si>
-    <t>2026-05-10T08:03:21.625Z</t>
-  </si>
-  <si>
-    <t>6a003cafae90c37e771e5019</t>
-  </si>
-  <si>
-    <t>Athar Golden Dome Heritage Watch</t>
-  </si>
-  <si>
-    <t>2026-05-10T08:07:10.984Z</t>
+    <t>2026-05-11T07:25:56.555Z</t>
   </si>
   <si>
     <t>6a003d4aae90c37e771e501b</t>
@@ -934,43 +1408,7 @@
     <t>Athar Tiberias Golden Mesh Watch</t>
   </si>
   <si>
-    <t>2026-05-10T08:09:46.205Z</t>
-  </si>
-  <si>
-    <t>6a003efdae90c37e771e501d</t>
-  </si>
-  <si>
-    <t>The Everlasting Bloom Motif.</t>
-  </si>
-  <si>
-    <t>2026-05-10T08:17:01.304Z</t>
-  </si>
-  <si>
-    <t>6a004120ae90c37e771e501f</t>
-  </si>
-  <si>
-    <t>Athar Jaffa Sunset Watch</t>
-  </si>
-  <si>
-    <t>2026-05-10T08:26:08.316Z</t>
-  </si>
-  <si>
-    <t>6a0041e5ae90c37e771e5021</t>
-  </si>
-  <si>
-    <t>Athar Bethlehem Dove of Peace Watch</t>
-  </si>
-  <si>
-    <t>2026-05-10T08:29:25.686Z</t>
-  </si>
-  <si>
-    <t>6a004302ae90c37e771e5023</t>
-  </si>
-  <si>
-    <t>Athar Ramallah Starry Horizon Watch</t>
-  </si>
-  <si>
-    <t>2026-05-10T08:34:10.136Z</t>
+    <t>2026-05-11T07:25:59.329Z</t>
   </si>
   <si>
     <t>Date</t>
@@ -1013,6 +1451,9 @@
   </si>
   <si>
     <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
   </si>
 </sst>
 </file>
@@ -1398,13 +1839,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="13" width="26" customWidth="1"/>
@@ -1474,10 +1916,10 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -1489,12 +1931,12 @@
         <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -1506,19 +1948,19 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="I3">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -1527,15 +1969,15 @@
         <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1547,10 +1989,10 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1571,12 +2013,12 @@
         <v>27</v>
       </c>
       <c r="M4" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -1588,10 +2030,10 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1612,12 +2054,12 @@
         <v>27</v>
       </c>
       <c r="M5" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1626,7 +2068,7 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -1638,10 +2080,10 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I6">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -1653,12 +2095,12 @@
         <v>32</v>
       </c>
       <c r="M6" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1667,7 +2109,7 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -1676,13 +2118,13 @@
         <v>18</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I7">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -1691,15 +2133,15 @@
         <v>20</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M7" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1708,22 +2150,22 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I8">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -1732,10 +2174,10 @@
         <v>20</v>
       </c>
       <c r="L8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" t="s">
         <v>36</v>
-      </c>
-      <c r="M8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1743,60 +2185,60 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" t="s">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>150</v>
+      </c>
+      <c r="I9">
+        <v>150</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>120</v>
-      </c>
-      <c r="I9">
-        <v>120</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1808,77 +2250,77 @@
         <v>150</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K10" t="s">
         <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>60</v>
+      </c>
+      <c r="I11">
+        <v>60</v>
+      </c>
+      <c r="J11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" t="s">
         <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>106</v>
-      </c>
-      <c r="I11">
-        <v>106</v>
-      </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
         <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1890,159 +2332,159 @@
         <v>150</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K12" t="s">
         <v>20</v>
       </c>
       <c r="L12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I13">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K13" t="s">
         <v>20</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M13" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="I14">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="J14" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s">
         <v>20</v>
       </c>
       <c r="L14" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M14" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="I15">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="J15" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K15" t="s">
         <v>20</v>
       </c>
       <c r="L15" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="M15" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
         <v>38</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F16" t="s">
         <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -2054,385 +2496,385 @@
         <v>150</v>
       </c>
       <c r="J16" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K16" t="s">
         <v>20</v>
       </c>
       <c r="L16" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="M16" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="I17">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="J17" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K17" t="s">
         <v>20</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="M17" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="I18">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="J18" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K18" t="s">
         <v>20</v>
       </c>
       <c r="L18" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19">
         <v>120</v>
       </c>
       <c r="J19" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K19" t="s">
         <v>20</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="M19" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
+        <v>150</v>
+      </c>
+      <c r="I20">
+        <v>150</v>
+      </c>
+      <c r="J20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" t="s">
+        <v>74</v>
+      </c>
+      <c r="M20" t="s">
         <v>75</v>
-      </c>
-      <c r="I20">
-        <v>75</v>
-      </c>
-      <c r="J20" t="s">
-        <v>41</v>
-      </c>
-      <c r="K20" t="s">
-        <v>20</v>
-      </c>
-      <c r="L20" t="s">
-        <v>78</v>
-      </c>
-      <c r="M20" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="I21">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="J21" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s">
         <v>20</v>
       </c>
       <c r="L21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I22">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K22" t="s">
         <v>20</v>
       </c>
       <c r="L22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="M22" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="I23">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="J23" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K23" t="s">
         <v>20</v>
       </c>
       <c r="L23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>67</v>
+      </c>
+      <c r="I24">
+        <v>67</v>
+      </c>
+      <c r="J24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" t="s">
         <v>90</v>
       </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>120</v>
-      </c>
-      <c r="I24">
-        <v>120</v>
-      </c>
-      <c r="J24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K24" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>91</v>
-      </c>
-      <c r="M24" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>150</v>
+      </c>
+      <c r="I25">
+        <v>150</v>
+      </c>
+      <c r="J25" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" t="s">
         <v>93</v>
       </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>120</v>
-      </c>
-      <c r="I25">
-        <v>120</v>
-      </c>
-      <c r="J25" t="s">
-        <v>85</v>
-      </c>
-      <c r="K25" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>94</v>
-      </c>
-      <c r="M25" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -2440,31 +2882,31 @@
         <v>95</v>
       </c>
       <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" t="s">
         <v>38</v>
       </c>
-      <c r="C26" t="s">
+      <c r="F26" t="s">
         <v>39</v>
       </c>
-      <c r="D26" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" t="s">
-        <v>26</v>
-      </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I26">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="J26" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K26" t="s">
         <v>20</v>
@@ -2473,147 +2915,147 @@
         <v>96</v>
       </c>
       <c r="M26" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="F27" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="I27">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s">
         <v>20</v>
       </c>
       <c r="L27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M27" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="I28">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K28" t="s">
         <v>20</v>
       </c>
       <c r="L28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M28" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="I29">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s">
         <v>20</v>
       </c>
       <c r="L29" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="M29" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -2622,36 +3064,36 @@
         <v>1</v>
       </c>
       <c r="H30">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="I30">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s">
         <v>20</v>
       </c>
       <c r="L30" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M30" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -2663,707 +3105,707 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I31">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="J31" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K31" t="s">
         <v>20</v>
       </c>
       <c r="L31" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="M31" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="I32">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="J32" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s">
         <v>20</v>
       </c>
       <c r="L32" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="M32" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="F33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J33" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s">
         <v>20</v>
       </c>
       <c r="L33" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="M33" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I34">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J34" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K34" t="s">
         <v>20</v>
       </c>
       <c r="L34" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M34" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" t="s">
         <v>38</v>
       </c>
-      <c r="C35" t="s">
+      <c r="F35" t="s">
         <v>39</v>
       </c>
-      <c r="D35" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" t="s">
-        <v>29</v>
-      </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I35">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="J35" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K35" t="s">
         <v>20</v>
       </c>
       <c r="L35" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M35" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I36">
-        <v>345</v>
+        <v>120</v>
       </c>
       <c r="J36" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K36" t="s">
         <v>20</v>
       </c>
       <c r="L36" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="M36" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I37">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J37" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K37" t="s">
         <v>20</v>
       </c>
       <c r="L37" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M37" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I38">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J38" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K38" t="s">
         <v>20</v>
       </c>
       <c r="L38" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="M38" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="I39">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="J39" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s">
         <v>20</v>
       </c>
       <c r="L39" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G40">
         <v>1</v>
       </c>
       <c r="H40">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I40">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J40" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K40" t="s">
         <v>20</v>
       </c>
       <c r="L40" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="M40" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" t="s">
         <v>38</v>
       </c>
-      <c r="C41" t="s">
+      <c r="F41" t="s">
         <v>39</v>
       </c>
-      <c r="D41" t="s">
-        <v>40</v>
-      </c>
-      <c r="E41" t="s">
-        <v>55</v>
-      </c>
-      <c r="F41" t="s">
-        <v>23</v>
-      </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="I41">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="J41" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K41" t="s">
         <v>20</v>
       </c>
       <c r="L41" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M41" t="s">
-        <v>15</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" t="s">
         <v>38</v>
       </c>
-      <c r="C42" t="s">
+      <c r="F42" t="s">
         <v>39</v>
       </c>
-      <c r="D42" t="s">
-        <v>40</v>
-      </c>
-      <c r="E42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" t="s">
-        <v>23</v>
-      </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="I42">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="J42" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K42" t="s">
         <v>20</v>
       </c>
       <c r="L42" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="M42" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E43" t="s">
         <v>38</v>
       </c>
-      <c r="C43" t="s">
+      <c r="F43" t="s">
         <v>39</v>
       </c>
-      <c r="D43" t="s">
-        <v>40</v>
-      </c>
-      <c r="E43" t="s">
-        <v>28</v>
-      </c>
-      <c r="F43" t="s">
-        <v>29</v>
-      </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I43">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="J43" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K43" t="s">
         <v>20</v>
       </c>
       <c r="L43" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="M43" t="s">
-        <v>15</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="B44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" t="s">
+        <v>70</v>
+      </c>
+      <c r="E44" t="s">
         <v>38</v>
       </c>
-      <c r="C44" t="s">
+      <c r="F44" t="s">
         <v>39</v>
       </c>
-      <c r="D44" t="s">
-        <v>40</v>
-      </c>
-      <c r="E44" t="s">
-        <v>55</v>
-      </c>
-      <c r="F44" t="s">
-        <v>23</v>
-      </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="I44">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="J44" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s">
         <v>20</v>
       </c>
       <c r="L44" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="M44" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="F45" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <v>60</v>
       </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>50</v>
-      </c>
       <c r="I45">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J45" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s">
         <v>20</v>
       </c>
       <c r="L45" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="M45" t="s">
-        <v>15</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E46" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="F46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I46">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J46" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K46" t="s">
         <v>20</v>
       </c>
       <c r="L46" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="M46" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E47" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F47" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="I47">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="J47" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K47" t="s">
         <v>20</v>
       </c>
       <c r="L47" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="M47" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E48" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="I48">
-        <v>94</v>
+        <v>345</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -3372,92 +3814,1568 @@
         <v>20</v>
       </c>
       <c r="L48" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="M48" t="s">
-        <v>15</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="F49" t="s">
+        <v>30</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <v>60</v>
       </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-      <c r="H49">
-        <v>50</v>
-      </c>
       <c r="I49">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J49" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s">
         <v>20</v>
       </c>
       <c r="L49" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="M49" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" t="s">
+        <v>30</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>60</v>
+      </c>
+      <c r="I50">
+        <v>60</v>
+      </c>
+      <c r="J50" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" t="s">
+        <v>171</v>
+      </c>
+      <c r="M50" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>173</v>
+      </c>
+      <c r="B51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" t="s">
+        <v>174</v>
+      </c>
+      <c r="F51" t="s">
+        <v>89</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>50</v>
+      </c>
+      <c r="I51">
+        <v>50</v>
+      </c>
+      <c r="J51" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" t="s">
+        <v>20</v>
+      </c>
+      <c r="L51" t="s">
+        <v>175</v>
+      </c>
+      <c r="M51" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>177</v>
+      </c>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" t="s">
+        <v>70</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>60</v>
+      </c>
+      <c r="I52">
+        <v>60</v>
+      </c>
+      <c r="J52" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" t="s">
+        <v>20</v>
+      </c>
+      <c r="L52" t="s">
+        <v>178</v>
+      </c>
+      <c r="M52" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>180</v>
+      </c>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" t="s">
+        <v>70</v>
+      </c>
+      <c r="E53" t="s">
+        <v>84</v>
+      </c>
+      <c r="F53" t="s">
+        <v>53</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>95</v>
+      </c>
+      <c r="I53">
+        <v>95</v>
+      </c>
+      <c r="J53" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" t="s">
+        <v>20</v>
+      </c>
+      <c r="L53" t="s">
+        <v>181</v>
+      </c>
+      <c r="M53" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>183</v>
+      </c>
+      <c r="B54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" t="s">
+        <v>70</v>
+      </c>
+      <c r="E54" t="s">
+        <v>52</v>
+      </c>
+      <c r="F54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>94</v>
+      </c>
+      <c r="I54">
+        <v>94</v>
+      </c>
+      <c r="J54" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" t="s">
+        <v>20</v>
+      </c>
+      <c r="L54" t="s">
+        <v>184</v>
+      </c>
+      <c r="M54" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>186</v>
+      </c>
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55" t="s">
+        <v>30</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>60</v>
+      </c>
+      <c r="I55">
+        <v>60</v>
+      </c>
+      <c r="J55" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" t="s">
+        <v>20</v>
+      </c>
+      <c r="L55" t="s">
+        <v>187</v>
+      </c>
+      <c r="M55" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>189</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" t="s">
+        <v>84</v>
+      </c>
+      <c r="F56" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>95</v>
+      </c>
+      <c r="I56">
+        <v>95</v>
+      </c>
+      <c r="J56" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" t="s">
+        <v>20</v>
+      </c>
+      <c r="L56" t="s">
+        <v>190</v>
+      </c>
+      <c r="M56" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>192</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" t="s">
+        <v>70</v>
+      </c>
+      <c r="E57" t="s">
+        <v>174</v>
+      </c>
+      <c r="F57" t="s">
+        <v>89</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>50</v>
+      </c>
+      <c r="I57">
+        <v>50</v>
+      </c>
+      <c r="J57" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" t="s">
+        <v>193</v>
+      </c>
+      <c r="M57" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>195</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" t="s">
+        <v>196</v>
+      </c>
+      <c r="F58" t="s">
+        <v>30</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>66</v>
+      </c>
+      <c r="I58">
+        <v>66</v>
+      </c>
+      <c r="J58" t="s">
+        <v>19</v>
+      </c>
+      <c r="K58" t="s">
+        <v>20</v>
+      </c>
+      <c r="L58" t="s">
+        <v>197</v>
+      </c>
+      <c r="M58" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59" t="s">
+        <v>53</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>94</v>
+      </c>
+      <c r="I59">
+        <v>94</v>
+      </c>
+      <c r="J59" t="s">
+        <v>19</v>
+      </c>
+      <c r="K59" t="s">
+        <v>20</v>
+      </c>
+      <c r="L59" t="s">
+        <v>200</v>
+      </c>
+      <c r="M59" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>202</v>
+      </c>
+      <c r="B60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" t="s">
+        <v>70</v>
+      </c>
+      <c r="E60" t="s">
+        <v>52</v>
+      </c>
+      <c r="F60" t="s">
+        <v>53</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>94</v>
+      </c>
+      <c r="I60">
+        <v>94</v>
+      </c>
+      <c r="J60" t="s">
+        <v>19</v>
+      </c>
+      <c r="K60" t="s">
+        <v>20</v>
+      </c>
+      <c r="L60" t="s">
+        <v>203</v>
+      </c>
+      <c r="M60" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>205</v>
+      </c>
+      <c r="B61" t="s">
+        <v>49</v>
+      </c>
+      <c r="C61" t="s">
+        <v>106</v>
+      </c>
+      <c r="D61" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" t="s">
+        <v>174</v>
+      </c>
+      <c r="F61" t="s">
+        <v>89</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>50</v>
+      </c>
+      <c r="I61">
+        <v>50</v>
+      </c>
+      <c r="J61" t="s">
+        <v>19</v>
+      </c>
+      <c r="K61" t="s">
+        <v>20</v>
+      </c>
+      <c r="L61" t="s">
+        <v>206</v>
+      </c>
+      <c r="M61" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>208</v>
+      </c>
+      <c r="B62" t="s">
+        <v>49</v>
+      </c>
+      <c r="C62" t="s">
+        <v>106</v>
+      </c>
+      <c r="D62" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62" t="s">
+        <v>38</v>
+      </c>
+      <c r="F62" t="s">
+        <v>39</v>
+      </c>
+      <c r="G62">
+        <v>8</v>
+      </c>
+      <c r="H62">
+        <v>150</v>
+      </c>
+      <c r="I62">
+        <v>1200</v>
+      </c>
+      <c r="J62" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" t="s">
+        <v>20</v>
+      </c>
+      <c r="L62" t="s">
+        <v>209</v>
+      </c>
+      <c r="M62" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>211</v>
+      </c>
+      <c r="B63" t="s">
+        <v>212</v>
+      </c>
+      <c r="C63" t="s">
+        <v>213</v>
+      </c>
+      <c r="D63" t="s">
+        <v>214</v>
+      </c>
+      <c r="E63" t="s">
+        <v>163</v>
+      </c>
+      <c r="F63" t="s">
+        <v>164</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>115</v>
+      </c>
+      <c r="I63">
+        <v>115</v>
+      </c>
+      <c r="J63" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" t="s">
+        <v>20</v>
+      </c>
+      <c r="L63" t="s">
+        <v>215</v>
+      </c>
+      <c r="M63" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>211</v>
+      </c>
+      <c r="B64" t="s">
+        <v>212</v>
+      </c>
+      <c r="C64" t="s">
+        <v>213</v>
+      </c>
+      <c r="D64" t="s">
+        <v>214</v>
+      </c>
+      <c r="E64" t="s">
+        <v>217</v>
+      </c>
+      <c r="F64" t="s">
+        <v>164</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>120</v>
+      </c>
+      <c r="I64">
+        <v>120</v>
+      </c>
+      <c r="J64" t="s">
+        <v>19</v>
+      </c>
+      <c r="K64" t="s">
+        <v>20</v>
+      </c>
+      <c r="L64" t="s">
+        <v>215</v>
+      </c>
+      <c r="M64" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>211</v>
+      </c>
+      <c r="B65" t="s">
+        <v>212</v>
+      </c>
+      <c r="C65" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" t="s">
+        <v>214</v>
+      </c>
+      <c r="E65" t="s">
+        <v>218</v>
+      </c>
+      <c r="F65" t="s">
+        <v>164</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>120</v>
+      </c>
+      <c r="I65">
+        <v>120</v>
+      </c>
+      <c r="J65" t="s">
+        <v>19</v>
+      </c>
+      <c r="K65" t="s">
+        <v>20</v>
+      </c>
+      <c r="L65" t="s">
+        <v>215</v>
+      </c>
+      <c r="M65" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>219</v>
+      </c>
+      <c r="B66" t="s">
+        <v>212</v>
+      </c>
+      <c r="C66" t="s">
+        <v>213</v>
+      </c>
+      <c r="D66" t="s">
+        <v>214</v>
+      </c>
+      <c r="E66" t="s">
+        <v>220</v>
+      </c>
+      <c r="F66" t="s">
+        <v>164</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>120</v>
+      </c>
+      <c r="I66">
+        <v>120</v>
+      </c>
+      <c r="J66" t="s">
+        <v>19</v>
+      </c>
+      <c r="K66" t="s">
+        <v>20</v>
+      </c>
+      <c r="L66" t="s">
+        <v>221</v>
+      </c>
+      <c r="M66" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>219</v>
+      </c>
+      <c r="B67" t="s">
+        <v>212</v>
+      </c>
+      <c r="C67" t="s">
+        <v>213</v>
+      </c>
+      <c r="D67" t="s">
+        <v>214</v>
+      </c>
+      <c r="E67" t="s">
+        <v>223</v>
+      </c>
+      <c r="F67" t="s">
+        <v>164</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>120</v>
+      </c>
+      <c r="I67">
+        <v>120</v>
+      </c>
+      <c r="J67" t="s">
+        <v>19</v>
+      </c>
+      <c r="K67" t="s">
+        <v>20</v>
+      </c>
+      <c r="L67" t="s">
+        <v>221</v>
+      </c>
+      <c r="M67" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>219</v>
+      </c>
+      <c r="B68" t="s">
+        <v>212</v>
+      </c>
+      <c r="C68" t="s">
+        <v>213</v>
+      </c>
+      <c r="D68" t="s">
+        <v>214</v>
+      </c>
+      <c r="E68" t="s">
+        <v>224</v>
+      </c>
+      <c r="F68" t="s">
+        <v>164</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>120</v>
+      </c>
+      <c r="I68">
+        <v>120</v>
+      </c>
+      <c r="J68" t="s">
+        <v>19</v>
+      </c>
+      <c r="K68" t="s">
+        <v>20</v>
+      </c>
+      <c r="L68" t="s">
+        <v>221</v>
+      </c>
+      <c r="M68" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>219</v>
+      </c>
+      <c r="B69" t="s">
+        <v>212</v>
+      </c>
+      <c r="C69" t="s">
+        <v>213</v>
+      </c>
+      <c r="D69" t="s">
+        <v>214</v>
+      </c>
+      <c r="E69" t="s">
+        <v>225</v>
+      </c>
+      <c r="F69" t="s">
+        <v>164</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>120</v>
+      </c>
+      <c r="I69">
+        <v>120</v>
+      </c>
+      <c r="J69" t="s">
+        <v>19</v>
+      </c>
+      <c r="K69" t="s">
+        <v>20</v>
+      </c>
+      <c r="L69" t="s">
+        <v>221</v>
+      </c>
+      <c r="M69" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" t="s">
+        <v>228</v>
+      </c>
+      <c r="D70" t="s">
+        <v>229</v>
+      </c>
+      <c r="E70" t="s">
+        <v>230</v>
+      </c>
+      <c r="F70" t="s">
+        <v>39</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>40</v>
+      </c>
+      <c r="I70">
+        <v>40</v>
+      </c>
+      <c r="J70" t="s">
+        <v>19</v>
+      </c>
+      <c r="K70" t="s">
+        <v>20</v>
+      </c>
+      <c r="L70" t="s">
+        <v>231</v>
+      </c>
+      <c r="M70" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>233</v>
+      </c>
+      <c r="B71" t="s">
+        <v>227</v>
+      </c>
+      <c r="C71" t="s">
+        <v>228</v>
+      </c>
+      <c r="D71" t="s">
+        <v>229</v>
+      </c>
+      <c r="E71" t="s">
+        <v>234</v>
+      </c>
+      <c r="F71" t="s">
+        <v>39</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
         <v>148</v>
       </c>
-      <c r="B50" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" t="s">
-        <v>77</v>
-      </c>
-      <c r="D50" t="s">
-        <v>31</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="I71">
+        <v>148</v>
+      </c>
+      <c r="J71" t="s">
+        <v>19</v>
+      </c>
+      <c r="K71" t="s">
+        <v>20</v>
+      </c>
+      <c r="L71" t="s">
+        <v>235</v>
+      </c>
+      <c r="M71" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>237</v>
+      </c>
+      <c r="B72" t="s">
+        <v>238</v>
+      </c>
+      <c r="C72" t="s">
+        <v>239</v>
+      </c>
+      <c r="D72" t="s">
+        <v>240</v>
+      </c>
+      <c r="E72" t="s">
+        <v>38</v>
+      </c>
+      <c r="F72" t="s">
+        <v>39</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>150</v>
+      </c>
+      <c r="I72">
+        <v>150</v>
+      </c>
+      <c r="J72" t="s">
+        <v>19</v>
+      </c>
+      <c r="K72" t="s">
+        <v>20</v>
+      </c>
+      <c r="L72" t="s">
+        <v>241</v>
+      </c>
+      <c r="M72" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" t="s">
+        <v>239</v>
+      </c>
+      <c r="D73" t="s">
+        <v>240</v>
+      </c>
+      <c r="E73" t="s">
+        <v>243</v>
+      </c>
+      <c r="F73" t="s">
+        <v>39</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>40</v>
+      </c>
+      <c r="I73">
+        <v>40</v>
+      </c>
+      <c r="J73" t="s">
+        <v>19</v>
+      </c>
+      <c r="K73" t="s">
+        <v>20</v>
+      </c>
+      <c r="L73" t="s">
+        <v>241</v>
+      </c>
+      <c r="M73" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>237</v>
+      </c>
+      <c r="B74" t="s">
+        <v>238</v>
+      </c>
+      <c r="C74" t="s">
+        <v>239</v>
+      </c>
+      <c r="D74" t="s">
+        <v>240</v>
+      </c>
+      <c r="E74" t="s">
+        <v>244</v>
+      </c>
+      <c r="F74" t="s">
+        <v>39</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>40</v>
+      </c>
+      <c r="I74">
+        <v>40</v>
+      </c>
+      <c r="J74" t="s">
+        <v>19</v>
+      </c>
+      <c r="K74" t="s">
+        <v>20</v>
+      </c>
+      <c r="L74" t="s">
+        <v>241</v>
+      </c>
+      <c r="M74" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>237</v>
+      </c>
+      <c r="B75" t="s">
+        <v>238</v>
+      </c>
+      <c r="C75" t="s">
+        <v>239</v>
+      </c>
+      <c r="D75" t="s">
+        <v>240</v>
+      </c>
+      <c r="E75" t="s">
+        <v>245</v>
+      </c>
+      <c r="F75" t="s">
+        <v>39</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>40</v>
+      </c>
+      <c r="I75">
+        <v>40</v>
+      </c>
+      <c r="J75" t="s">
+        <v>19</v>
+      </c>
+      <c r="K75" t="s">
+        <v>20</v>
+      </c>
+      <c r="L75" t="s">
+        <v>241</v>
+      </c>
+      <c r="M75" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>237</v>
+      </c>
+      <c r="B76" t="s">
+        <v>238</v>
+      </c>
+      <c r="C76" t="s">
+        <v>239</v>
+      </c>
+      <c r="D76" t="s">
+        <v>240</v>
+      </c>
+      <c r="E76" t="s">
+        <v>246</v>
+      </c>
+      <c r="F76" t="s">
+        <v>39</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>40</v>
+      </c>
+      <c r="I76">
+        <v>40</v>
+      </c>
+      <c r="J76" t="s">
+        <v>19</v>
+      </c>
+      <c r="K76" t="s">
+        <v>20</v>
+      </c>
+      <c r="L76" t="s">
+        <v>241</v>
+      </c>
+      <c r="M76" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>247</v>
+      </c>
+      <c r="B77" t="s">
+        <v>238</v>
+      </c>
+      <c r="C77" t="s">
+        <v>239</v>
+      </c>
+      <c r="D77" t="s">
+        <v>240</v>
+      </c>
+      <c r="E77" t="s">
+        <v>234</v>
+      </c>
+      <c r="F77" t="s">
+        <v>39</v>
+      </c>
+      <c r="G77">
+        <v>3</v>
+      </c>
+      <c r="H77">
+        <v>148</v>
+      </c>
+      <c r="I77">
+        <v>444</v>
+      </c>
+      <c r="J77" t="s">
+        <v>19</v>
+      </c>
+      <c r="K77" t="s">
+        <v>20</v>
+      </c>
+      <c r="L77" t="s">
+        <v>248</v>
+      </c>
+      <c r="M77" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>247</v>
+      </c>
+      <c r="B78" t="s">
+        <v>238</v>
+      </c>
+      <c r="C78" t="s">
+        <v>239</v>
+      </c>
+      <c r="D78" t="s">
+        <v>240</v>
+      </c>
+      <c r="E78" t="s">
+        <v>244</v>
+      </c>
+      <c r="F78" t="s">
+        <v>39</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>40</v>
+      </c>
+      <c r="I78">
+        <v>40</v>
+      </c>
+      <c r="J78" t="s">
+        <v>19</v>
+      </c>
+      <c r="K78" t="s">
+        <v>20</v>
+      </c>
+      <c r="L78" t="s">
+        <v>248</v>
+      </c>
+      <c r="M78" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>247</v>
+      </c>
+      <c r="B79" t="s">
+        <v>238</v>
+      </c>
+      <c r="C79" t="s">
+        <v>239</v>
+      </c>
+      <c r="D79" t="s">
+        <v>240</v>
+      </c>
+      <c r="E79" t="s">
+        <v>243</v>
+      </c>
+      <c r="F79" t="s">
+        <v>39</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>40</v>
+      </c>
+      <c r="I79">
+        <v>40</v>
+      </c>
+      <c r="J79" t="s">
+        <v>19</v>
+      </c>
+      <c r="K79" t="s">
+        <v>20</v>
+      </c>
+      <c r="L79" t="s">
+        <v>248</v>
+      </c>
+      <c r="M79" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>250</v>
+      </c>
+      <c r="B80" t="s">
+        <v>238</v>
+      </c>
+      <c r="C80" t="s">
+        <v>239</v>
+      </c>
+      <c r="D80" t="s">
+        <v>240</v>
+      </c>
+      <c r="E80" t="s">
         <v>17</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F80" t="s">
         <v>18</v>
       </c>
-      <c r="G50">
-        <v>8</v>
-      </c>
-      <c r="H50">
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>120</v>
+      </c>
+      <c r="I80">
+        <v>120</v>
+      </c>
+      <c r="J80" t="s">
+        <v>19</v>
+      </c>
+      <c r="K80" t="s">
+        <v>20</v>
+      </c>
+      <c r="L80" t="s">
+        <v>251</v>
+      </c>
+      <c r="M80" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" t="s">
+        <v>238</v>
+      </c>
+      <c r="C81" t="s">
+        <v>239</v>
+      </c>
+      <c r="D81" t="s">
+        <v>240</v>
+      </c>
+      <c r="E81" t="s">
+        <v>253</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>25</v>
+      </c>
+      <c r="I81">
+        <v>25</v>
+      </c>
+      <c r="J81" t="s">
+        <v>19</v>
+      </c>
+      <c r="K81" t="s">
+        <v>20</v>
+      </c>
+      <c r="L81" t="s">
+        <v>251</v>
+      </c>
+      <c r="M81" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>250</v>
+      </c>
+      <c r="B82" t="s">
+        <v>238</v>
+      </c>
+      <c r="C82" t="s">
+        <v>239</v>
+      </c>
+      <c r="D82" t="s">
+        <v>240</v>
+      </c>
+      <c r="E82" t="s">
+        <v>174</v>
+      </c>
+      <c r="F82" t="s">
+        <v>89</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>50</v>
+      </c>
+      <c r="I82">
+        <v>100</v>
+      </c>
+      <c r="J82" t="s">
+        <v>19</v>
+      </c>
+      <c r="K82" t="s">
+        <v>20</v>
+      </c>
+      <c r="L82" t="s">
+        <v>251</v>
+      </c>
+      <c r="M82" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>250</v>
+      </c>
+      <c r="B83" t="s">
+        <v>238</v>
+      </c>
+      <c r="C83" t="s">
+        <v>239</v>
+      </c>
+      <c r="D83" t="s">
+        <v>240</v>
+      </c>
+      <c r="E83" t="s">
+        <v>88</v>
+      </c>
+      <c r="F83" t="s">
+        <v>89</v>
+      </c>
+      <c r="G83">
+        <v>3</v>
+      </c>
+      <c r="H83">
+        <v>67</v>
+      </c>
+      <c r="I83">
+        <v>201</v>
+      </c>
+      <c r="J83" t="s">
+        <v>19</v>
+      </c>
+      <c r="K83" t="s">
+        <v>20</v>
+      </c>
+      <c r="L83" t="s">
+        <v>251</v>
+      </c>
+      <c r="M83" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>254</v>
+      </c>
+      <c r="B84" t="s">
+        <v>255</v>
+      </c>
+      <c r="C84" t="s">
+        <v>256</v>
+      </c>
+      <c r="D84" t="s">
+        <v>257</v>
+      </c>
+      <c r="E84" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>120</v>
+      </c>
+      <c r="I84">
+        <v>120</v>
+      </c>
+      <c r="J84" t="s">
+        <v>19</v>
+      </c>
+      <c r="K84" t="s">
+        <v>20</v>
+      </c>
+      <c r="L84" t="s">
+        <v>258</v>
+      </c>
+      <c r="M84" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>254</v>
+      </c>
+      <c r="B85" t="s">
+        <v>255</v>
+      </c>
+      <c r="C85" t="s">
+        <v>256</v>
+      </c>
+      <c r="D85" t="s">
+        <v>257</v>
+      </c>
+      <c r="E85" t="s">
+        <v>38</v>
+      </c>
+      <c r="F85" t="s">
+        <v>39</v>
+      </c>
+      <c r="G85">
+        <v>3</v>
+      </c>
+      <c r="H85">
         <v>150</v>
       </c>
-      <c r="I50">
-        <v>1200</v>
-      </c>
-      <c r="J50" t="s">
-        <v>41</v>
-      </c>
-      <c r="K50" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" t="s">
-        <v>149</v>
-      </c>
-      <c r="M50" t="s">
-        <v>150</v>
+      <c r="I85">
+        <v>450</v>
+      </c>
+      <c r="J85" t="s">
+        <v>19</v>
+      </c>
+      <c r="K85" t="s">
+        <v>20</v>
+      </c>
+      <c r="L85" t="s">
+        <v>258</v>
+      </c>
+      <c r="M85" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>254</v>
+      </c>
+      <c r="B86" t="s">
+        <v>255</v>
+      </c>
+      <c r="C86" t="s">
+        <v>256</v>
+      </c>
+      <c r="D86" t="s">
+        <v>257</v>
+      </c>
+      <c r="E86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86" t="s">
+        <v>30</v>
+      </c>
+      <c r="G86">
+        <v>2</v>
+      </c>
+      <c r="H86">
+        <v>60</v>
+      </c>
+      <c r="I86">
+        <v>120</v>
+      </c>
+      <c r="J86" t="s">
+        <v>19</v>
+      </c>
+      <c r="K86" t="s">
+        <v>20</v>
+      </c>
+      <c r="L86" t="s">
+        <v>258</v>
+      </c>
+      <c r="M86" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -3468,11 +5386,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="6" width="16" customWidth="1"/>
     <col min="7" max="8" width="26" customWidth="1"/>
@@ -3482,112 +5400,112 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>260</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>153</v>
+        <v>262</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>154</v>
+        <v>263</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>155</v>
+        <v>264</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>156</v>
+        <v>265</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>158</v>
+        <v>267</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>159</v>
+        <v>268</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>160</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>1645</v>
+        <v>1788</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="H2" t="s">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>163</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>464</v>
+        <v>1645</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>273</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="J3" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -3596,144 +5514,336 @@
         <v>630</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="J4" t="s">
-        <v>163</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>274</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>239</v>
       </c>
       <c r="D5" t="s">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1340</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>275</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>276</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>169</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>255</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>257</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>278</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>278</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J6" t="s">
-        <v>169</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>280</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>281</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J7" t="s">
-        <v>169</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>283</v>
       </c>
       <c r="B8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" t="s">
+        <v>214</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>875</v>
+      </c>
+      <c r="G8" t="s">
+        <v>284</v>
+      </c>
+      <c r="H8" t="s">
+        <v>285</v>
+      </c>
+      <c r="I8" t="s">
+        <v>164</v>
+      </c>
+      <c r="J8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" t="s">
+        <v>294</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" t="s">
+        <v>292</v>
+      </c>
+      <c r="C11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D11" t="s">
+        <v>297</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" t="s">
+        <v>299</v>
+      </c>
+      <c r="D12" t="s">
+        <v>297</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" t="s">
+        <v>302</v>
+      </c>
+      <c r="D13" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14">
         <v>38</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F14">
+        <v>4730</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
+        <v>305</v>
+      </c>
+      <c r="I14" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>4590</v>
-      </c>
-      <c r="G8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" t="s">
-        <v>176</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>163</v>
+      <c r="J14" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3757,7 +5867,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -3766,709 +5876,709 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>178</v>
+        <v>307</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>179</v>
+        <v>308</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>180</v>
+        <v>309</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>181</v>
+        <v>310</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>182</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>312</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>3150</v>
+        <v>4050</v>
       </c>
       <c r="G2" t="s">
-        <v>184</v>
+        <v>313</v>
       </c>
       <c r="H2" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>186</v>
+        <v>315</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>1080</v>
+        <v>2040</v>
       </c>
       <c r="G3" t="s">
-        <v>187</v>
+        <v>316</v>
       </c>
       <c r="H3" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>188</v>
+        <v>317</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>169</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="G4" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="H4" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>319</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>376</v>
+        <v>592</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>320</v>
       </c>
       <c r="H5" t="s">
-        <v>192</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>193</v>
+        <v>321</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>345</v>
+        <v>460</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="H6" t="s">
-        <v>192</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>285</v>
+        <v>376</v>
       </c>
       <c r="G7" t="s">
-        <v>195</v>
+        <v>324</v>
       </c>
       <c r="H7" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>325</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>165</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>212</v>
+        <v>285</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>326</v>
       </c>
       <c r="H8" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>328</v>
       </c>
       <c r="H9" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>88</v>
+        <v>250</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>330</v>
       </c>
       <c r="H10" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>332</v>
       </c>
       <c r="H11" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>333</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>223</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>133</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>334</v>
       </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>335</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>156</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>336</v>
       </c>
       <c r="H13" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>337</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>338</v>
       </c>
       <c r="H14" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>204</v>
+        <v>339</v>
       </c>
       <c r="B15" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="H15" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>341</v>
       </c>
       <c r="B16" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>342</v>
       </c>
       <c r="H16" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>343</v>
       </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>129</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>344</v>
       </c>
       <c r="H17" t="s">
-        <v>192</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>345</v>
       </c>
       <c r="B18" t="s">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>149</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="H18" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>212</v>
+        <v>347</v>
       </c>
       <c r="B19" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>348</v>
       </c>
       <c r="H19" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>214</v>
+        <v>349</v>
       </c>
       <c r="B20" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="H20" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>216</v>
+        <v>351</v>
       </c>
       <c r="B21" t="s">
-        <v>217</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>352</v>
       </c>
       <c r="H21" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>218</v>
+        <v>353</v>
       </c>
       <c r="B22" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>354</v>
       </c>
       <c r="H22" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>220</v>
+        <v>355</v>
       </c>
       <c r="B23" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>356</v>
       </c>
       <c r="H23" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>222</v>
+        <v>357</v>
       </c>
       <c r="B24" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>358</v>
       </c>
       <c r="H24" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>224</v>
+        <v>359</v>
       </c>
       <c r="B25" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>360</v>
       </c>
       <c r="H25" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>226</v>
+        <v>361</v>
       </c>
       <c r="B26" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>362</v>
       </c>
       <c r="H26" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>228</v>
+        <v>363</v>
       </c>
       <c r="B27" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>364</v>
       </c>
       <c r="H27" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>230</v>
+        <v>365</v>
       </c>
       <c r="B28" t="s">
-        <v>231</v>
+        <v>366</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D28">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4477,24 +6587,24 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>367</v>
       </c>
       <c r="H28" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>232</v>
+        <v>368</v>
       </c>
       <c r="B29" t="s">
-        <v>233</v>
+        <v>369</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4503,24 +6613,24 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="H29" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>234</v>
+        <v>371</v>
       </c>
       <c r="B30" t="s">
-        <v>235</v>
+        <v>372</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4529,24 +6639,24 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>373</v>
       </c>
       <c r="H30" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>236</v>
+        <v>374</v>
       </c>
       <c r="B31" t="s">
-        <v>237</v>
+        <v>375</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4555,24 +6665,24 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>376</v>
       </c>
       <c r="H31" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>238</v>
+        <v>377</v>
       </c>
       <c r="B32" t="s">
-        <v>239</v>
+        <v>378</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4581,24 +6691,24 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>379</v>
       </c>
       <c r="H32" t="s">
-        <v>192</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>241</v>
+        <v>381</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -4607,24 +6717,24 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>382</v>
       </c>
       <c r="H33" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>242</v>
+        <v>383</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>384</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D34">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -4633,24 +6743,24 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>385</v>
       </c>
       <c r="H34" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>244</v>
+        <v>386</v>
       </c>
       <c r="B35" t="s">
-        <v>245</v>
+        <v>387</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -4659,24 +6769,24 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>388</v>
       </c>
       <c r="H35" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>246</v>
+        <v>389</v>
       </c>
       <c r="B36" t="s">
-        <v>247</v>
+        <v>390</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -4685,24 +6795,24 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>391</v>
       </c>
       <c r="H36" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>248</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s">
-        <v>249</v>
+        <v>393</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -4711,24 +6821,24 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>394</v>
       </c>
       <c r="H37" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s">
-        <v>251</v>
+        <v>396</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>164</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -4737,24 +6847,24 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>397</v>
       </c>
       <c r="H38" t="s">
-        <v>192</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>252</v>
+        <v>398</v>
       </c>
       <c r="B39" t="s">
-        <v>253</v>
+        <v>399</v>
       </c>
       <c r="C39" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -4763,24 +6873,24 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>254</v>
+        <v>400</v>
       </c>
       <c r="H39" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>255</v>
+        <v>401</v>
       </c>
       <c r="B40" t="s">
-        <v>256</v>
+        <v>402</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D40">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -4789,24 +6899,24 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>257</v>
+        <v>403</v>
       </c>
       <c r="H40" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>258</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s">
-        <v>259</v>
+        <v>405</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -4815,24 +6925,24 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>260</v>
+        <v>406</v>
       </c>
       <c r="H41" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>261</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s">
-        <v>262</v>
+        <v>408</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -4841,24 +6951,24 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>263</v>
+        <v>409</v>
       </c>
       <c r="H42" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>264</v>
+        <v>410</v>
       </c>
       <c r="B43" t="s">
-        <v>265</v>
+        <v>411</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -4867,24 +6977,24 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>266</v>
+        <v>412</v>
       </c>
       <c r="H43" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>267</v>
+        <v>413</v>
       </c>
       <c r="B44" t="s">
-        <v>268</v>
+        <v>414</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -4893,24 +7003,24 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>269</v>
+        <v>415</v>
       </c>
       <c r="H44" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>270</v>
+        <v>416</v>
       </c>
       <c r="B45" t="s">
-        <v>271</v>
+        <v>417</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -4919,24 +7029,24 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>272</v>
+        <v>418</v>
       </c>
       <c r="H45" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>273</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s">
-        <v>274</v>
+        <v>420</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -4945,24 +7055,24 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>275</v>
+        <v>421</v>
       </c>
       <c r="H46" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>276</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s">
-        <v>277</v>
+        <v>423</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -4971,24 +7081,24 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>278</v>
+        <v>424</v>
       </c>
       <c r="H47" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>279</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s">
-        <v>280</v>
+        <v>426</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>164</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -4997,24 +7107,24 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>281</v>
+        <v>427</v>
       </c>
       <c r="H48" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>282</v>
+        <v>428</v>
       </c>
       <c r="B49" t="s">
-        <v>283</v>
+        <v>429</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -5023,24 +7133,24 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>284</v>
+        <v>430</v>
       </c>
       <c r="H49" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>285</v>
+        <v>431</v>
       </c>
       <c r="B50" t="s">
-        <v>286</v>
+        <v>432</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -5049,24 +7159,24 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>287</v>
+        <v>433</v>
       </c>
       <c r="H50" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>288</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s">
-        <v>289</v>
+        <v>435</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -5075,24 +7185,24 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>290</v>
+        <v>436</v>
       </c>
       <c r="H51" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>291</v>
+        <v>437</v>
       </c>
       <c r="B52" t="s">
-        <v>292</v>
+        <v>438</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -5101,24 +7211,24 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>293</v>
+        <v>439</v>
       </c>
       <c r="H52" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>294</v>
+        <v>440</v>
       </c>
       <c r="B53" t="s">
-        <v>295</v>
+        <v>441</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -5127,24 +7237,24 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>296</v>
+        <v>442</v>
       </c>
       <c r="H53" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>297</v>
+        <v>443</v>
       </c>
       <c r="B54" t="s">
-        <v>295</v>
+        <v>444</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -5153,24 +7263,24 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>298</v>
+        <v>445</v>
       </c>
       <c r="H54" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>299</v>
+        <v>446</v>
       </c>
       <c r="B55" t="s">
-        <v>295</v>
+        <v>447</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -5179,24 +7289,24 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>300</v>
+        <v>448</v>
       </c>
       <c r="H55" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>301</v>
+        <v>449</v>
       </c>
       <c r="B56" t="s">
-        <v>302</v>
+        <v>450</v>
       </c>
       <c r="C56" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -5205,24 +7315,24 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>303</v>
+        <v>451</v>
       </c>
       <c r="H56" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>304</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s">
-        <v>305</v>
+        <v>453</v>
       </c>
       <c r="C57" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -5231,24 +7341,24 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>306</v>
+        <v>454</v>
       </c>
       <c r="H57" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>307</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s">
-        <v>308</v>
+        <v>456</v>
       </c>
       <c r="C58" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D58">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -5257,24 +7367,24 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>309</v>
+        <v>457</v>
       </c>
       <c r="H58" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>310</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s">
-        <v>311</v>
+        <v>253</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -5283,50 +7393,50 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>312</v>
+        <v>459</v>
       </c>
       <c r="H59" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>313</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s">
+        <v>253</v>
+      </c>
+      <c r="C60" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60">
+        <v>122</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>461</v>
+      </c>
+      <c r="H60" t="s">
         <v>314</v>
-      </c>
-      <c r="C60" t="s">
-        <v>117</v>
-      </c>
-      <c r="D60">
-        <v>10</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60" t="s">
-        <v>315</v>
-      </c>
-      <c r="H60" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>316</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s">
-        <v>317</v>
+        <v>463</v>
       </c>
       <c r="C61" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -5335,10 +7445,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>318</v>
+        <v>464</v>
       </c>
       <c r="H61" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -5349,7 +7459,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -5360,30 +7470,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>465</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>320</v>
+        <v>466</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
+        <v>264</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>321</v>
+        <v>467</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>322</v>
+        <v>468</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>268</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>323</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>324</v>
+        <v>470</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -5395,10 +7505,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G2">
         <v>232</v>
@@ -5406,7 +7516,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>325</v>
+        <v>471</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -5418,10 +7528,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G3">
         <v>210</v>
@@ -5429,7 +7539,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>472</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -5441,10 +7551,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G4">
         <v>141.18</v>
@@ -5452,7 +7562,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -5464,10 +7574,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="G5">
         <v>64</v>
@@ -5475,7 +7585,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>328</v>
+        <v>474</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -5487,10 +7597,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>140</v>
@@ -5498,7 +7608,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>475</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -5510,10 +7620,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G7">
         <v>170</v>
@@ -5521,7 +7631,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>476</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -5533,10 +7643,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G8">
         <v>140</v>
@@ -5544,7 +7654,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>477</v>
       </c>
       <c r="B9">
         <v>2738</v>
@@ -5556,10 +7666,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G9">
         <v>119.04</v>
@@ -5567,7 +7677,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>478</v>
       </c>
       <c r="B10">
         <v>1290</v>
@@ -5579,13 +7689,36 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G10">
         <v>645</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>479</v>
+      </c>
+      <c r="B11">
+        <v>4617</v>
+      </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11">
+        <v>256.5</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="510">
   <si>
     <t>Order ID</t>
   </si>
@@ -796,6 +796,51 @@
     <t>2026-05-11T15:18:07.976Z</t>
   </si>
   <si>
+    <t>ATH8422721553</t>
+  </si>
+  <si>
+    <t>Athar Earthly Heritage Bucket Bag</t>
+  </si>
+  <si>
+    <t>2026-05-14T18:43:47.220Z</t>
+  </si>
+  <si>
+    <t>2026-05-14T18:44:44.430Z</t>
+  </si>
+  <si>
+    <t>ATH8812358459</t>
+  </si>
+  <si>
+    <t>2026-05-14T19:48:43.588Z</t>
+  </si>
+  <si>
+    <t>2026-05-14T19:52:16.897Z</t>
+  </si>
+  <si>
+    <t>ATH8839643111</t>
+  </si>
+  <si>
+    <t>2026-05-14T19:53:16.434Z</t>
+  </si>
+  <si>
+    <t>2026-05-14T19:54:28.189Z</t>
+  </si>
+  <si>
+    <t>ATH9182840060</t>
+  </si>
+  <si>
+    <t>Confirmed</t>
+  </si>
+  <si>
+    <t>2026-05-14T20:50:28.405Z</t>
+  </si>
+  <si>
+    <t>ATH9682985879</t>
+  </si>
+  <si>
+    <t>2026-05-14T22:13:49.861Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -835,7 +880,7 @@
     <t>69df51939a28b213c15d5bfb</t>
   </si>
   <si>
-    <t>2026-05-06T17:59:46.019Z</t>
+    <t>2026-05-14T20:50:29.121Z</t>
   </si>
   <si>
     <t>6a01bbfa695111dcf9655902</t>
@@ -853,6 +898,54 @@
     <t>2026-05-11T15:16:45.171Z</t>
   </si>
   <si>
+    <t>6a038d695b1f5e1c2b0969d8</t>
+  </si>
+  <si>
+    <t>Demo Customer</t>
+  </si>
+  <si>
+    <t>demo.customer@athar.local</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>6a039294695111dcf9656ec6</t>
+  </si>
+  <si>
+    <t>Demo Gaza Customer</t>
+  </si>
+  <si>
+    <t>demo.gaza@athar.local</t>
+  </si>
+  <si>
+    <t>6a039293695111dcf9656ec5</t>
+  </si>
+  <si>
+    <t>Demo Hebron Customer</t>
+  </si>
+  <si>
+    <t>demo.hebron@athar.local</t>
+  </si>
+  <si>
+    <t>6a039293695111dcf9656ec4</t>
+  </si>
+  <si>
+    <t>Demo Nablus Customer</t>
+  </si>
+  <si>
+    <t>demo.nablus@athar.local</t>
+  </si>
+  <si>
+    <t>6a039294695111dcf9656ec7</t>
+  </si>
+  <si>
+    <t>Demo Ramallah Customer</t>
+  </si>
+  <si>
+    <t>demo.ramallah@athar.local</t>
+  </si>
+  <si>
     <t>6a01ba79695111dcf96558e5</t>
   </si>
   <si>
@@ -886,9 +979,6 @@
     <t>+970592434550</t>
   </si>
   <si>
-    <t>New</t>
-  </si>
-  <si>
     <t>69d8d572ae6a1e8c2c032bc2</t>
   </si>
   <si>
@@ -931,7 +1021,7 @@
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
-    <t>2026-05-11T10:25:59.379Z</t>
+    <t>2026-05-14T22:13:50.323Z</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -1015,6 +1105,12 @@
     <t>2026-05-11T07:26:27.694Z</t>
   </si>
   <si>
+    <t>69ff852f61b6c73a91e2da71</t>
+  </si>
+  <si>
+    <t>2026-05-11T07:25:32.191Z</t>
+  </si>
+  <si>
     <t>69f20e78c49efb1805c2fc83</t>
   </si>
   <si>
@@ -1345,15 +1441,6 @@
     <t>2026-05-11T07:25:31.505Z</t>
   </si>
   <si>
-    <t>69ff852f61b6c73a91e2da71</t>
-  </si>
-  <si>
-    <t>Athar Earthly Heritage Bucket Bag</t>
-  </si>
-  <si>
-    <t>2026-05-11T07:25:32.191Z</t>
-  </si>
-  <si>
     <t>69ff8a3f61b6c73a91e2da7e</t>
   </si>
   <si>
@@ -1454,6 +1541,9 @@
   </si>
   <si>
     <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
   </si>
 </sst>
 </file>
@@ -1839,7 +1929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -5378,6 +5468,211 @@
         <v>259</v>
       </c>
     </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>260</v>
+      </c>
+      <c r="B87" t="s">
+        <v>49</v>
+      </c>
+      <c r="C87" t="s">
+        <v>106</v>
+      </c>
+      <c r="D87" t="s">
+        <v>58</v>
+      </c>
+      <c r="E87" t="s">
+        <v>261</v>
+      </c>
+      <c r="F87" t="s">
+        <v>39</v>
+      </c>
+      <c r="G87">
+        <v>4</v>
+      </c>
+      <c r="H87">
+        <v>40</v>
+      </c>
+      <c r="I87">
+        <v>160</v>
+      </c>
+      <c r="J87" t="s">
+        <v>19</v>
+      </c>
+      <c r="K87" t="s">
+        <v>20</v>
+      </c>
+      <c r="L87" t="s">
+        <v>262</v>
+      </c>
+      <c r="M87" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>264</v>
+      </c>
+      <c r="B88" t="s">
+        <v>68</v>
+      </c>
+      <c r="C88" t="s">
+        <v>69</v>
+      </c>
+      <c r="D88" t="s">
+        <v>70</v>
+      </c>
+      <c r="E88" t="s">
+        <v>38</v>
+      </c>
+      <c r="F88" t="s">
+        <v>39</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>150</v>
+      </c>
+      <c r="I88">
+        <v>150</v>
+      </c>
+      <c r="J88" t="s">
+        <v>19</v>
+      </c>
+      <c r="K88" t="s">
+        <v>20</v>
+      </c>
+      <c r="L88" t="s">
+        <v>265</v>
+      </c>
+      <c r="M88" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>267</v>
+      </c>
+      <c r="B89" t="s">
+        <v>68</v>
+      </c>
+      <c r="C89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" t="s">
+        <v>70</v>
+      </c>
+      <c r="E89" t="s">
+        <v>38</v>
+      </c>
+      <c r="F89" t="s">
+        <v>39</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>150</v>
+      </c>
+      <c r="I89">
+        <v>150</v>
+      </c>
+      <c r="J89" t="s">
+        <v>19</v>
+      </c>
+      <c r="K89" t="s">
+        <v>20</v>
+      </c>
+      <c r="L89" t="s">
+        <v>268</v>
+      </c>
+      <c r="M89" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>270</v>
+      </c>
+      <c r="B90" t="s">
+        <v>49</v>
+      </c>
+      <c r="C90" t="s">
+        <v>106</v>
+      </c>
+      <c r="D90" t="s">
+        <v>58</v>
+      </c>
+      <c r="E90" t="s">
+        <v>38</v>
+      </c>
+      <c r="F90" t="s">
+        <v>39</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>150</v>
+      </c>
+      <c r="I90">
+        <v>150</v>
+      </c>
+      <c r="J90" t="s">
+        <v>271</v>
+      </c>
+      <c r="K90" t="s">
+        <v>20</v>
+      </c>
+      <c r="L90" t="s">
+        <v>272</v>
+      </c>
+      <c r="M90" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>273</v>
+      </c>
+      <c r="B91" t="s">
+        <v>68</v>
+      </c>
+      <c r="C91" t="s">
+        <v>69</v>
+      </c>
+      <c r="D91" t="s">
+        <v>70</v>
+      </c>
+      <c r="E91" t="s">
+        <v>38</v>
+      </c>
+      <c r="F91" t="s">
+        <v>39</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>150</v>
+      </c>
+      <c r="I91">
+        <v>150</v>
+      </c>
+      <c r="J91" t="s">
+        <v>271</v>
+      </c>
+      <c r="K91" t="s">
+        <v>20</v>
+      </c>
+      <c r="L91" t="s">
+        <v>274</v>
+      </c>
+      <c r="M91" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5386,7 +5681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -5400,34 +5695,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -5453,18 +5748,18 @@
         <v>50</v>
       </c>
       <c r="H2" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -5476,22 +5771,22 @@
         <v>58</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1645</v>
+        <v>1995</v>
       </c>
       <c r="G3" t="s">
         <v>107</v>
       </c>
       <c r="H3" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="I3" t="s">
         <v>39</v>
       </c>
       <c r="J3" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -5523,12 +5818,12 @@
         <v>39</v>
       </c>
       <c r="J4" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="B5" t="s">
         <v>238</v>
@@ -5546,21 +5841,21 @@
         <v>1340</v>
       </c>
       <c r="G5" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="H5" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="I5" t="s">
         <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B6" t="s">
         <v>255</v>
@@ -5578,94 +5873,94 @@
         <v>710</v>
       </c>
       <c r="G6" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="H6" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="I6" t="s">
         <v>39</v>
       </c>
       <c r="J6" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>296</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>280</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>281</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="D8" t="s">
-        <v>214</v>
+        <v>257</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>284</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>285</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>164</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="D9" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5683,21 +5978,21 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B10" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C10" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="D10" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5715,21 +6010,21 @@
         <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B11" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="C11" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D11" t="s">
-        <v>297</v>
+        <v>257</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5747,103 +6042,263 @@
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>227</v>
       </c>
       <c r="C12" t="s">
-        <v>299</v>
+        <v>228</v>
       </c>
       <c r="D12" t="s">
-        <v>297</v>
+        <v>229</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>311</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>312</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J12" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B13" t="s">
-        <v>301</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="D13" t="s">
-        <v>303</v>
+        <v>214</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>315</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>316</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="J13" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B14" t="s">
+        <v>318</v>
+      </c>
+      <c r="C14" t="s">
+        <v>319</v>
+      </c>
+      <c r="D14" t="s">
+        <v>320</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" t="s">
+        <v>322</v>
+      </c>
+      <c r="C15" t="s">
+        <v>323</v>
+      </c>
+      <c r="D15" t="s">
+        <v>324</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>325</v>
+      </c>
+      <c r="B16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C16" t="s">
+        <v>326</v>
+      </c>
+      <c r="D16" t="s">
+        <v>327</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B17" t="s">
+        <v>322</v>
+      </c>
+      <c r="C17" t="s">
+        <v>329</v>
+      </c>
+      <c r="D17" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>330</v>
+      </c>
+      <c r="B18" t="s">
+        <v>331</v>
+      </c>
+      <c r="C18" t="s">
+        <v>332</v>
+      </c>
+      <c r="D18" t="s">
+        <v>333</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>334</v>
+      </c>
+      <c r="B19" t="s">
         <v>68</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C19" t="s">
         <v>69</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D19" t="s">
         <v>70</v>
       </c>
-      <c r="E14">
-        <v>38</v>
-      </c>
-      <c r="F14">
-        <v>4730</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="E19">
+        <v>41</v>
+      </c>
+      <c r="F19">
+        <v>5240</v>
+      </c>
+      <c r="G19" t="s">
         <v>71</v>
       </c>
-      <c r="H14" t="s">
-        <v>305</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="H19" t="s">
+        <v>335</v>
+      </c>
+      <c r="I19" t="s">
         <v>39</v>
       </c>
-      <c r="J14" t="s">
-        <v>271</v>
+      <c r="J19" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -5867,7 +6322,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -5876,24 +6331,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="B2" t="s">
         <v>38</v>
@@ -5902,24 +6357,24 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>4050</v>
+        <v>4650</v>
       </c>
       <c r="G2" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="H2" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -5937,15 +6392,15 @@
         <v>2040</v>
       </c>
       <c r="G3" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="H3" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
         <v>29</v>
@@ -5963,15 +6418,15 @@
         <v>900</v>
       </c>
       <c r="G4" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="H4" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="B5" t="s">
         <v>234</v>
@@ -5989,15 +6444,15 @@
         <v>592</v>
       </c>
       <c r="G5" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="H5" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="B6" t="s">
         <v>163</v>
@@ -6015,15 +6470,15 @@
         <v>460</v>
       </c>
       <c r="G6" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="H6" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -6041,15 +6496,15 @@
         <v>376</v>
       </c>
       <c r="G7" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="H7" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="B8" t="s">
         <v>84</v>
@@ -6067,15 +6522,15 @@
         <v>285</v>
       </c>
       <c r="G8" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="H8" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="B9" t="s">
         <v>88</v>
@@ -6093,15 +6548,15 @@
         <v>268</v>
       </c>
       <c r="G9" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="H9" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="B10" t="s">
         <v>174</v>
@@ -6119,15 +6574,15 @@
         <v>250</v>
       </c>
       <c r="G10" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="H10" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="B11" t="s">
         <v>77</v>
@@ -6145,50 +6600,50 @@
         <v>212</v>
       </c>
       <c r="G11" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="H11" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>39</v>
       </c>
       <c r="D12">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G12" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="H12" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="B13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C13" t="s">
         <v>164</v>
       </c>
       <c r="D13">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -6197,24 +6652,24 @@
         <v>120</v>
       </c>
       <c r="G13" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="H13" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="B14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
         <v>164</v>
       </c>
       <c r="D14">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -6223,24 +6678,24 @@
         <v>120</v>
       </c>
       <c r="G14" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="H14" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="B15" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C15" t="s">
         <v>164</v>
       </c>
       <c r="D15">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -6249,24 +6704,24 @@
         <v>120</v>
       </c>
       <c r="G15" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="H15" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
         <v>164</v>
       </c>
       <c r="D16">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -6275,24 +6730,24 @@
         <v>120</v>
       </c>
       <c r="G16" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="H16" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="B17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C17" t="s">
         <v>164</v>
       </c>
       <c r="D17">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -6301,76 +6756,76 @@
         <v>120</v>
       </c>
       <c r="G17" t="s">
+        <v>374</v>
+      </c>
+      <c r="H17" t="s">
         <v>344</v>
-      </c>
-      <c r="H17" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="D18">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="G18" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="H18" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="B19" t="s">
-        <v>243</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D19">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="H19" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="B20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
         <v>39</v>
       </c>
       <c r="D20">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -6379,128 +6834,128 @@
         <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="H20" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>244</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D21">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="H21" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D22">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="H22" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s">
         <v>30</v>
       </c>
       <c r="D23">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="H23" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="B24" t="s">
-        <v>245</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D24">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="H24" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="B25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C25" t="s">
         <v>39</v>
       </c>
       <c r="D25">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -6509,24 +6964,24 @@
         <v>40</v>
       </c>
       <c r="G25" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="H25" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="B26" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="C26" t="s">
         <v>39</v>
       </c>
       <c r="D26">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -6535,76 +6990,76 @@
         <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="H26" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="B27" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D27">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="H27" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="B28" t="s">
-        <v>366</v>
+        <v>253</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D28">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G28" t="s">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="H28" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="B29" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D29">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6613,24 +7068,24 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="H29" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="B30" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="D30">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6639,24 +7094,24 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="H30" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="B31" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="D31">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6665,24 +7120,24 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="H31" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="B32" t="s">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D32">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6691,24 +7146,24 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="H32" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="B33" t="s">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D33">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6717,24 +7172,24 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="H33" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>383</v>
+        <v>412</v>
       </c>
       <c r="B34" t="s">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="C34" t="s">
         <v>53</v>
       </c>
       <c r="D34">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6743,24 +7198,24 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>385</v>
+        <v>414</v>
       </c>
       <c r="H34" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="B35" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="C35" t="s">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="D35">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6769,24 +7224,24 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="H35" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="B36" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="C36" t="s">
         <v>164</v>
       </c>
       <c r="D36">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -6795,24 +7250,24 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="H36" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="B37" t="s">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="D37">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -6821,24 +7276,24 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="H37" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="B38" t="s">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D38">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -6847,24 +7302,24 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="H38" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="B39" t="s">
-        <v>399</v>
+        <v>428</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D39">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -6873,24 +7328,24 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="H39" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="B40" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="C40" t="s">
         <v>53</v>
       </c>
       <c r="D40">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -6899,24 +7354,24 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="H40" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>404</v>
+        <v>433</v>
       </c>
       <c r="B41" t="s">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="C41" t="s">
         <v>53</v>
       </c>
       <c r="D41">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6925,24 +7380,24 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>406</v>
+        <v>435</v>
       </c>
       <c r="H41" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="B42" t="s">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="C42" t="s">
         <v>53</v>
       </c>
       <c r="D42">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -6951,24 +7406,24 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="H42" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="B43" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="C43" t="s">
         <v>53</v>
       </c>
       <c r="D43">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -6977,24 +7432,24 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="H43" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>413</v>
+        <v>442</v>
       </c>
       <c r="B44" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="D44">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -7003,24 +7458,24 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="H44" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="B45" t="s">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="D45">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -7029,24 +7484,24 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>418</v>
+        <v>447</v>
       </c>
       <c r="H45" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="B46" t="s">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="C46" t="s">
         <v>30</v>
       </c>
       <c r="D46">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -7055,24 +7510,24 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="H46" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="B47" t="s">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="D47">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -7081,24 +7536,24 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>424</v>
+        <v>453</v>
       </c>
       <c r="H47" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="B48" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="D48">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -7107,24 +7562,24 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="H48" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>428</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="C49" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D49">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -7133,24 +7588,24 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="H49" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="B50" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D50">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -7159,24 +7614,24 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="H50" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="B51" t="s">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="C51" t="s">
         <v>53</v>
       </c>
       <c r="D51">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -7185,24 +7640,24 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
       <c r="H51" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="B52" t="s">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="C52" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D52">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -7211,24 +7666,24 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="H52" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="B53" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="C53" t="s">
         <v>39</v>
       </c>
       <c r="D53">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -7237,24 +7692,24 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="H53" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="C54" t="s">
         <v>39</v>
       </c>
       <c r="D54">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -7263,18 +7718,18 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="H54" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s">
-        <v>447</v>
+        <v>476</v>
       </c>
       <c r="C55" t="s">
         <v>39</v>
@@ -7289,18 +7744,18 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>448</v>
+        <v>477</v>
       </c>
       <c r="H55" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
       <c r="B56" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
@@ -7315,18 +7770,18 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="H56" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s">
-        <v>453</v>
+        <v>482</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
@@ -7341,18 +7796,18 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="H57" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>455</v>
+        <v>484</v>
       </c>
       <c r="B58" t="s">
-        <v>456</v>
+        <v>485</v>
       </c>
       <c r="C58" t="s">
         <v>18</v>
@@ -7367,15 +7822,15 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>457</v>
+        <v>486</v>
       </c>
       <c r="H58" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
       <c r="B59" t="s">
         <v>253</v>
@@ -7393,15 +7848,15 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>459</v>
+        <v>488</v>
       </c>
       <c r="H59" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>460</v>
+        <v>489</v>
       </c>
       <c r="B60" t="s">
         <v>253</v>
@@ -7419,18 +7874,18 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>461</v>
+        <v>490</v>
       </c>
       <c r="H60" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>462</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s">
-        <v>463</v>
+        <v>492</v>
       </c>
       <c r="C61" t="s">
         <v>164</v>
@@ -7445,10 +7900,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>464</v>
+        <v>493</v>
       </c>
       <c r="H61" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -7459,7 +7914,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -7470,30 +7925,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>465</v>
+        <v>494</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>466</v>
+        <v>495</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>467</v>
+        <v>496</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>468</v>
+        <v>497</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>469</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -7516,7 +7971,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>471</v>
+        <v>500</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -7539,7 +7994,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>472</v>
+        <v>501</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -7562,7 +8017,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>473</v>
+        <v>502</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -7585,7 +8040,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>474</v>
+        <v>503</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -7608,7 +8063,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>475</v>
+        <v>504</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -7631,7 +8086,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>476</v>
+        <v>505</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -7654,7 +8109,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="B9">
         <v>2738</v>
@@ -7677,7 +8132,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>478</v>
+        <v>507</v>
       </c>
       <c r="B10">
         <v>1290</v>
@@ -7700,7 +8155,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>479</v>
+        <v>508</v>
       </c>
       <c r="B11">
         <v>4617</v>
@@ -7719,6 +8174,29 @@
       </c>
       <c r="G11">
         <v>256.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>509</v>
+      </c>
+      <c r="B12">
+        <v>860</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sales_data.xlsx
+++ b/exports/sales_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="522">
   <si>
     <t>Order ID</t>
   </si>
@@ -841,6 +841,39 @@
     <t>2026-05-14T22:13:49.861Z</t>
   </si>
   <si>
+    <t>ATH7595791954</t>
+  </si>
+  <si>
+    <t>2026-05-15T20:12:37.922Z</t>
+  </si>
+  <si>
+    <t>2026-05-15T20:13:40.807Z</t>
+  </si>
+  <si>
+    <t>ATH7706482376</t>
+  </si>
+  <si>
+    <t>2026-05-15T20:31:04.826Z</t>
+  </si>
+  <si>
+    <t>2026-05-15T20:31:33.889Z</t>
+  </si>
+  <si>
+    <t>ATH8186550527</t>
+  </si>
+  <si>
+    <t>2026-05-15T21:51:05.508Z</t>
+  </si>
+  <si>
+    <t>2026-05-15T21:51:43.519Z</t>
+  </si>
+  <si>
+    <t>ATH8310472292</t>
+  </si>
+  <si>
+    <t>2026-05-15T22:11:44.724Z</t>
+  </si>
+  <si>
     <t>Customer ID</t>
   </si>
   <si>
@@ -880,7 +913,7 @@
     <t>69df51939a28b213c15d5bfb</t>
   </si>
   <si>
-    <t>2026-05-14T20:50:29.121Z</t>
+    <t>2026-05-15T20:31:05.543Z</t>
   </si>
   <si>
     <t>6a01bbfa695111dcf9655902</t>
@@ -1021,7 +1054,7 @@
     <t>69df56a29a28b213c15d5c44</t>
   </si>
   <si>
-    <t>2026-05-14T22:13:50.323Z</t>
+    <t>2026-05-15T22:11:45.187Z</t>
   </si>
   <si>
     <t>Product ID</t>
@@ -1544,6 +1577,9 @@
   </si>
   <si>
     <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
   </si>
 </sst>
 </file>
@@ -1929,7 +1965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -5670,6 +5706,170 @@
         <v>274</v>
       </c>
       <c r="M91" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>275</v>
+      </c>
+      <c r="B92" t="s">
+        <v>49</v>
+      </c>
+      <c r="C92" t="s">
+        <v>106</v>
+      </c>
+      <c r="D92" t="s">
+        <v>58</v>
+      </c>
+      <c r="E92" t="s">
+        <v>38</v>
+      </c>
+      <c r="F92" t="s">
+        <v>39</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>150</v>
+      </c>
+      <c r="I92">
+        <v>150</v>
+      </c>
+      <c r="J92" t="s">
+        <v>19</v>
+      </c>
+      <c r="K92" t="s">
+        <v>20</v>
+      </c>
+      <c r="L92" t="s">
+        <v>276</v>
+      </c>
+      <c r="M92" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>278</v>
+      </c>
+      <c r="B93" t="s">
+        <v>49</v>
+      </c>
+      <c r="C93" t="s">
+        <v>106</v>
+      </c>
+      <c r="D93" t="s">
+        <v>58</v>
+      </c>
+      <c r="E93" t="s">
+        <v>38</v>
+      </c>
+      <c r="F93" t="s">
+        <v>39</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>150</v>
+      </c>
+      <c r="I93">
+        <v>150</v>
+      </c>
+      <c r="J93" t="s">
+        <v>19</v>
+      </c>
+      <c r="K93" t="s">
+        <v>20</v>
+      </c>
+      <c r="L93" t="s">
+        <v>279</v>
+      </c>
+      <c r="M93" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>281</v>
+      </c>
+      <c r="B94" t="s">
+        <v>68</v>
+      </c>
+      <c r="C94" t="s">
+        <v>69</v>
+      </c>
+      <c r="D94" t="s">
+        <v>70</v>
+      </c>
+      <c r="E94" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" t="s">
+        <v>30</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>60</v>
+      </c>
+      <c r="I94">
+        <v>60</v>
+      </c>
+      <c r="J94" t="s">
+        <v>19</v>
+      </c>
+      <c r="K94" t="s">
+        <v>20</v>
+      </c>
+      <c r="L94" t="s">
+        <v>282</v>
+      </c>
+      <c r="M94" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>284</v>
+      </c>
+      <c r="B95" t="s">
+        <v>68</v>
+      </c>
+      <c r="C95" t="s">
+        <v>69</v>
+      </c>
+      <c r="D95" t="s">
+        <v>70</v>
+      </c>
+      <c r="E95" t="s">
+        <v>38</v>
+      </c>
+      <c r="F95" t="s">
+        <v>39</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>150</v>
+      </c>
+      <c r="I95">
+        <v>150</v>
+      </c>
+      <c r="J95" t="s">
+        <v>271</v>
+      </c>
+      <c r="K95" t="s">
+        <v>20</v>
+      </c>
+      <c r="L95" t="s">
+        <v>285</v>
+      </c>
+      <c r="M95" t="s">
         <v>15</v>
       </c>
     </row>
@@ -5695,34 +5895,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -5748,18 +5948,18 @@
         <v>50</v>
       </c>
       <c r="H2" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -5771,22 +5971,22 @@
         <v>58</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>1995</v>
+        <v>2245</v>
       </c>
       <c r="G3" t="s">
         <v>107</v>
       </c>
       <c r="H3" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="I3" t="s">
         <v>39</v>
       </c>
       <c r="J3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -5818,12 +6018,12 @@
         <v>39</v>
       </c>
       <c r="J4" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="B5" t="s">
         <v>238</v>
@@ -5841,21 +6041,21 @@
         <v>1340</v>
       </c>
       <c r="G5" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="H5" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="I5" t="s">
         <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B6" t="s">
         <v>255</v>
@@ -5873,27 +6073,27 @@
         <v>710</v>
       </c>
       <c r="G6" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="H6" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="I6" t="s">
         <v>39</v>
       </c>
       <c r="J6" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="B7" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C7" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D7" t="s">
         <v>257</v>
@@ -5914,18 +6114,18 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="B8" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C8" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="D8" t="s">
         <v>257</v>
@@ -5946,18 +6146,18 @@
         <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B9" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C9" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="D9" t="s">
         <v>257</v>
@@ -5978,18 +6178,18 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="B10" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C10" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="D10" t="s">
         <v>257</v>
@@ -6010,18 +6210,18 @@
         <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B11" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C11" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="D11" t="s">
         <v>257</v>
@@ -6042,12 +6242,12 @@
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B12" t="s">
         <v>227</v>
@@ -6065,21 +6265,21 @@
         <v>228</v>
       </c>
       <c r="G12" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="H12" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="I12" t="s">
         <v>39</v>
       </c>
       <c r="J12" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="B13" t="s">
         <v>212</v>
@@ -6097,30 +6297,30 @@
         <v>875</v>
       </c>
       <c r="G13" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="H13" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="I13" t="s">
         <v>164</v>
       </c>
       <c r="J13" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C14" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="D14" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6138,21 +6338,21 @@
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B15" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C15" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D15" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6170,21 +6370,21 @@
         <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C16" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="D16" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6202,21 +6402,21 @@
         <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B17" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C17" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D17" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6234,21 +6434,21 @@
         <v>15</v>
       </c>
       <c r="J17" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B18" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="C18" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="D18" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6266,12 +6466,12 @@
         <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B19" t="s">
         <v>68</v>
@@ -6283,22 +6483,22 @@
         <v>70</v>
       </c>
       <c r="E19">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F19">
-        <v>5240</v>
+        <v>5490</v>
       </c>
       <c r="G19" t="s">
         <v>71</v>
       </c>
       <c r="H19" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="I19" t="s">
         <v>39</v>
       </c>
       <c r="J19" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -6322,7 +6522,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -6331,24 +6531,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B2" t="s">
         <v>38</v>
@@ -6357,24 +6557,24 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>4650</v>
+        <v>5100</v>
       </c>
       <c r="G2" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="H2" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -6392,15 +6592,15 @@
         <v>2040</v>
       </c>
       <c r="G3" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="H3" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B4" t="s">
         <v>29</v>
@@ -6409,24 +6609,24 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>900</v>
+        <v>960</v>
       </c>
       <c r="G4" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="H4" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B5" t="s">
         <v>234</v>
@@ -6444,15 +6644,15 @@
         <v>592</v>
       </c>
       <c r="G5" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H5" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B6" t="s">
         <v>163</v>
@@ -6470,15 +6670,15 @@
         <v>460</v>
       </c>
       <c r="G6" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="H6" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -6496,15 +6696,15 @@
         <v>376</v>
       </c>
       <c r="G7" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H7" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B8" t="s">
         <v>84</v>
@@ -6522,15 +6722,15 @@
         <v>285</v>
       </c>
       <c r="G8" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="H8" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B9" t="s">
         <v>88</v>
@@ -6548,15 +6748,15 @@
         <v>268</v>
       </c>
       <c r="G9" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="H9" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B10" t="s">
         <v>174</v>
@@ -6574,15 +6774,15 @@
         <v>250</v>
       </c>
       <c r="G10" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="H10" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B11" t="s">
         <v>77</v>
@@ -6600,15 +6800,15 @@
         <v>212</v>
       </c>
       <c r="G11" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="H11" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B12" t="s">
         <v>261</v>
@@ -6626,15 +6826,15 @@
         <v>160</v>
       </c>
       <c r="G12" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H12" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B13" t="s">
         <v>223</v>
@@ -6652,15 +6852,15 @@
         <v>120</v>
       </c>
       <c r="G13" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H13" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B14" t="s">
         <v>224</v>
@@ -6678,15 +6878,15 @@
         <v>120</v>
       </c>
       <c r="G14" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H14" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B15" t="s">
         <v>225</v>
@@ -6704,15 +6904,15 @@
         <v>120</v>
       </c>
       <c r="G15" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="H15" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B16" t="s">
         <v>220</v>
@@ -6730,15 +6930,15 @@
         <v>120</v>
       </c>
       <c r="G16" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="H16" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B17" t="s">
         <v>218</v>
@@ -6756,15 +6956,15 @@
         <v>120</v>
       </c>
       <c r="G17" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="H17" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B18" t="s">
         <v>217</v>
@@ -6782,15 +6982,15 @@
         <v>120</v>
       </c>
       <c r="G18" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="H18" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="B19" t="s">
         <v>99</v>
@@ -6808,15 +7008,15 @@
         <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="H19" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B20" t="s">
         <v>243</v>
@@ -6834,15 +7034,15 @@
         <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="H20" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B21" t="s">
         <v>244</v>
@@ -6860,15 +7060,15 @@
         <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="H21" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
@@ -6886,15 +7086,15 @@
         <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="H22" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="B23" t="s">
         <v>196</v>
@@ -6912,15 +7112,15 @@
         <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="H23" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B24" t="s">
         <v>117</v>
@@ -6938,15 +7138,15 @@
         <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="H24" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B25" t="s">
         <v>245</v>
@@ -6964,15 +7164,15 @@
         <v>40</v>
       </c>
       <c r="G25" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="H25" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B26" t="s">
         <v>246</v>
@@ -6990,15 +7190,15 @@
         <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="H26" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B27" t="s">
         <v>230</v>
@@ -7016,15 +7216,15 @@
         <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="H27" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B28" t="s">
         <v>253</v>
@@ -7042,18 +7242,18 @@
         <v>25</v>
       </c>
       <c r="G28" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H28" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B29" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="C29" t="s">
         <v>53</v>
@@ -7068,18 +7268,18 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="H29" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B30" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="C30" t="s">
         <v>30</v>
@@ -7094,18 +7294,18 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="H30" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="B31" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="C31" t="s">
         <v>89</v>
@@ -7120,18 +7320,18 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="H31" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B32" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C32" t="s">
         <v>53</v>
@@ -7146,18 +7346,18 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="H32" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B33" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C33" t="s">
         <v>39</v>
@@ -7172,18 +7372,18 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="H33" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B34" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C34" t="s">
         <v>53</v>
@@ -7198,18 +7398,18 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="H34" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B35" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="C35" t="s">
         <v>53</v>
@@ -7224,18 +7424,18 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="H35" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B36" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C36" t="s">
         <v>164</v>
@@ -7250,18 +7450,18 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="H36" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B37" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C37" t="s">
         <v>164</v>
@@ -7276,18 +7476,18 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="H37" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B38" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C38" t="s">
         <v>30</v>
@@ -7302,18 +7502,18 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="H38" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="B39" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -7328,18 +7528,18 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="H39" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B40" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C40" t="s">
         <v>53</v>
@@ -7354,18 +7554,18 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="H40" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="B41" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="C41" t="s">
         <v>53</v>
@@ -7380,18 +7580,18 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="H41" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="B42" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C42" t="s">
         <v>53</v>
@@ -7406,18 +7606,18 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="H42" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="B43" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="C43" t="s">
         <v>53</v>
@@ -7432,18 +7632,18 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="H43" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="B44" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C44" t="s">
         <v>53</v>
@@ -7458,18 +7658,18 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="H44" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B45" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C45" t="s">
         <v>89</v>
@@ -7484,18 +7684,18 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="H45" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B46" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="C46" t="s">
         <v>30</v>
@@ -7510,18 +7710,18 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="H46" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B47" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C47" t="s">
         <v>30</v>
@@ -7536,18 +7736,18 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="H47" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B48" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="C48" t="s">
         <v>89</v>
@@ -7562,18 +7762,18 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="H48" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B49" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C49" t="s">
         <v>53</v>
@@ -7588,18 +7788,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="H49" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="B50" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
@@ -7614,18 +7814,18 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="H50" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="C51" t="s">
         <v>53</v>
@@ -7640,18 +7840,18 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="H51" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B52" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="C52" t="s">
         <v>53</v>
@@ -7666,18 +7866,18 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="H52" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="C53" t="s">
         <v>39</v>
@@ -7692,18 +7892,18 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="H53" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B54" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="C54" t="s">
         <v>39</v>
@@ -7718,18 +7918,18 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="H54" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B55" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="C55" t="s">
         <v>39</v>
@@ -7744,18 +7944,18 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="H55" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B56" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
@@ -7770,18 +7970,18 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="H56" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B57" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
@@ -7796,18 +7996,18 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="H57" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B58" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="C58" t="s">
         <v>18</v>
@@ -7822,15 +8022,15 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="H58" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B59" t="s">
         <v>253</v>
@@ -7848,15 +8048,15 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="H59" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B60" t="s">
         <v>253</v>
@@ -7874,18 +8074,18 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="H60" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B61" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C61" t="s">
         <v>164</v>
@@ -7900,10 +8100,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="H61" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -7914,7 +8114,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -7925,30 +8125,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B2">
         <v>464</v>
@@ -7971,7 +8171,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -7994,7 +8194,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B4">
         <v>1553</v>
@@ -8017,7 +8217,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -8040,7 +8240,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -8063,7 +8263,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="B7">
         <v>170</v>
@@ -8086,7 +8286,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -8109,7 +8309,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B9">
         <v>2738</v>
@@ -8132,7 +8332,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B10">
         <v>1290</v>
@@ -8155,7 +8355,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B11">
         <v>4617</v>
@@ -8178,7 +8378,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B12">
         <v>860</v>
@@ -8197,6 +8397,29 @@
       </c>
       <c r="G12">
         <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>521</v>
+      </c>
+      <c r="B13">
+        <v>500</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
